--- a/assets/characters/Character.xlsx
+++ b/assets/characters/Character.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\work\git\ScanMonster\assets\characters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C87E9145-4197-4A5F-8D77-8D79DB32F968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42BFA0A1-610B-4C3A-84A4-6D83483179BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ground" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1955" uniqueCount="959">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2001" uniqueCount="959">
   <si>
     <t>no</t>
   </si>
@@ -216,9 +216,6 @@
     <t>イグアナ</t>
   </si>
   <si>
-    <t>Iguana</t>
-  </si>
-  <si>
     <t>ジャガロン</t>
   </si>
   <si>
@@ -228,27 +225,18 @@
     <t>カンガルー</t>
   </si>
   <si>
-    <t>Kangaroo</t>
-  </si>
-  <si>
     <t>コアラン</t>
   </si>
   <si>
     <t>コアラ</t>
   </si>
   <si>
-    <t>Koala</t>
-  </si>
-  <si>
     <t>キツネザルン</t>
   </si>
   <si>
     <t>キツネザル</t>
   </si>
   <si>
-    <t>Lemur</t>
-  </si>
-  <si>
     <t>ヒョウテン</t>
   </si>
   <si>
@@ -270,9 +258,6 @@
     <t>トカゲ</t>
   </si>
   <si>
-    <t>Lizard</t>
-  </si>
-  <si>
     <t>ラマロン</t>
   </si>
   <si>
@@ -303,27 +288,18 @@
     <t>ミーアキャット</t>
   </si>
   <si>
-    <t>Meerkat</t>
-  </si>
-  <si>
     <t>モグリット</t>
   </si>
   <si>
     <t>モグラ</t>
   </si>
   <si>
-    <t>Mole</t>
-  </si>
-  <si>
     <t>サルッコ</t>
   </si>
   <si>
     <t>サル</t>
   </si>
   <si>
-    <t>Monkey</t>
-  </si>
-  <si>
     <t>ムースン</t>
   </si>
   <si>
@@ -336,9 +312,6 @@
     <t>ネズミ</t>
   </si>
   <si>
-    <t>Mouse</t>
-  </si>
-  <si>
     <t>オカピン</t>
   </si>
   <si>
@@ -363,189 +336,126 @@
     <t>ヤマアラシ</t>
   </si>
   <si>
-    <t>Porcupine</t>
-  </si>
-  <si>
     <t>プレリード</t>
   </si>
   <si>
     <t>プレーリードッグ</t>
   </si>
   <si>
-    <t>Prairie Dog</t>
-  </si>
-  <si>
     <t>ツキウサ</t>
   </si>
   <si>
     <t>うさぎ</t>
   </si>
   <si>
-    <t>Rabbit</t>
-  </si>
-  <si>
     <t>ホシアライ</t>
   </si>
   <si>
     <t>アライグマ</t>
   </si>
   <si>
-    <t>Raccoon</t>
-  </si>
-  <si>
     <t>マメタヌキ</t>
   </si>
   <si>
     <t>タヌキ</t>
   </si>
   <si>
-    <t>Raccoon Dog</t>
-  </si>
-  <si>
     <t>レッサン</t>
   </si>
   <si>
     <t>レッサーパンダ</t>
   </si>
   <si>
-    <t>Red Panda</t>
-  </si>
-  <si>
     <t>サイガン</t>
   </si>
   <si>
     <t>サイ</t>
   </si>
   <si>
-    <t>Rhinoceros</t>
-  </si>
-  <si>
     <t>カモシカゼ</t>
   </si>
   <si>
     <t>カモシカ</t>
   </si>
   <si>
-    <t>Serow</t>
-  </si>
-  <si>
     <t>ツノヒツジ</t>
   </si>
   <si>
     <t>羊</t>
   </si>
   <si>
-    <t>Sheep</t>
-  </si>
-  <si>
     <t>スカンクー</t>
   </si>
   <si>
     <t>スカンク</t>
   </si>
   <si>
-    <t>Skunk</t>
-  </si>
-  <si>
     <t>ナマケロン</t>
   </si>
   <si>
     <t>ナマケモノ</t>
   </si>
   <si>
-    <t>Sloth</t>
-  </si>
-  <si>
     <t>ヘビマキ</t>
   </si>
   <si>
     <t>ヘビ</t>
   </si>
   <si>
-    <t>Snake</t>
-  </si>
-  <si>
     <t>コノハリス</t>
   </si>
   <si>
     <t>リス</t>
   </si>
   <si>
-    <t>Squirrel</t>
-  </si>
-  <si>
     <t>バクミィ</t>
   </si>
   <si>
     <t>バク</t>
   </si>
   <si>
-    <t>Tapir</t>
-  </si>
-  <si>
     <t>トラマル</t>
   </si>
   <si>
     <t>トラ</t>
   </si>
   <si>
-    <t>Tiger</t>
-  </si>
-  <si>
     <t>ビクーニャル</t>
   </si>
   <si>
     <t>ビクーニャ</t>
   </si>
   <si>
-    <t>Vicuna</t>
-  </si>
-  <si>
     <t>イタチル</t>
   </si>
   <si>
     <t>イタチ</t>
   </si>
   <si>
-    <t>Weasel</t>
-  </si>
-  <si>
     <t>イノマル</t>
   </si>
   <si>
     <t>イノシシ</t>
   </si>
   <si>
-    <t>Wild Boar</t>
-  </si>
-  <si>
     <t>オオカミン</t>
   </si>
   <si>
     <t>オオカミ</t>
   </si>
   <si>
-    <t>Wolf</t>
-  </si>
-  <si>
     <t>シマウマル</t>
   </si>
   <si>
     <t>シマウマ</t>
   </si>
   <si>
-    <t>Zebra</t>
-  </si>
-  <si>
     <t>センザンコ</t>
   </si>
   <si>
     <t>センザンコウ</t>
   </si>
   <si>
-    <t>Pangolin</t>
-  </si>
-  <si>
     <t>ツチブタン</t>
   </si>
   <si>
@@ -559,9 +469,6 @@
   </si>
   <si>
     <t>トナカイ</t>
-  </si>
-  <si>
-    <t>Reindeer</t>
   </si>
   <si>
     <t>フェンリル</t>
@@ -2949,6 +2856,130 @@
   </si>
   <si>
     <t>No</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Iguana</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Kangaroo</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Koala</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Lemur</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Lizard</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Meerkat</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Mole</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Monkey</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Mouse</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pangolin</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Porcupine</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Prairie Dog</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Rabbit</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Raccoon</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Raccoon Dog</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Red Panda</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Reindeer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Rhinoceros</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Serow</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Sheep</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Skunk</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Sloth</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Snake</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Squirrel</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Tapir</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Tiger</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Vicuna</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Weasel</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Wild Boar</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Wolf</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Zebra</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3350,7 +3381,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
-        <v>958</v>
+        <v>927</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -3376,19 +3407,19 @@
         <v>67</v>
       </c>
       <c r="B2" t="s">
-        <v>172</v>
+        <v>142</v>
       </c>
       <c r="C2" t="s">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="D2" t="s">
-        <v>918</v>
+        <v>887</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>957</v>
+        <v>926</v>
       </c>
       <c r="G2" t="s">
         <v>11</v>
@@ -3405,13 +3436,13 @@
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>938</v>
+        <v>907</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>957</v>
+        <v>926</v>
       </c>
       <c r="G3" t="s">
         <v>11</v>
@@ -3428,13 +3459,13 @@
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>939</v>
+        <v>908</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>957</v>
+        <v>926</v>
       </c>
       <c r="G4" t="s">
         <v>11</v>
@@ -3451,13 +3482,13 @@
         <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>940</v>
+        <v>909</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>957</v>
+        <v>926</v>
       </c>
       <c r="G5" t="s">
         <v>11</v>
@@ -3471,16 +3502,16 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>917</v>
+        <v>886</v>
       </c>
       <c r="D6" t="s">
-        <v>919</v>
+        <v>888</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>957</v>
+        <v>926</v>
       </c>
       <c r="G6" t="s">
         <v>11</v>
@@ -3497,13 +3528,13 @@
         <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>941</v>
+        <v>910</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>957</v>
+        <v>926</v>
       </c>
       <c r="G7" t="s">
         <v>11</v>
@@ -3514,19 +3545,19 @@
         <v>68</v>
       </c>
       <c r="B8" t="s">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="C8" t="s">
-        <v>920</v>
+        <v>889</v>
       </c>
       <c r="D8" t="s">
-        <v>921</v>
+        <v>890</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>957</v>
+        <v>926</v>
       </c>
       <c r="G8" t="s">
         <v>11</v>
@@ -3543,13 +3574,13 @@
         <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>942</v>
+        <v>911</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>957</v>
+        <v>926</v>
       </c>
       <c r="G9" t="s">
         <v>11</v>
@@ -3566,13 +3597,13 @@
         <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>943</v>
+        <v>912</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>957</v>
+        <v>926</v>
       </c>
       <c r="G10" t="s">
         <v>11</v>
@@ -3589,13 +3620,13 @@
         <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>944</v>
+        <v>913</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>957</v>
+        <v>926</v>
       </c>
       <c r="G11" t="s">
         <v>11</v>
@@ -3612,13 +3643,13 @@
         <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>945</v>
+        <v>914</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>957</v>
+        <v>926</v>
       </c>
       <c r="G12" t="s">
         <v>11</v>
@@ -3632,16 +3663,16 @@
         <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>922</v>
+        <v>891</v>
       </c>
       <c r="D13" t="s">
-        <v>923</v>
+        <v>892</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>957</v>
+        <v>926</v>
       </c>
       <c r="G13" t="s">
         <v>11</v>
@@ -3658,13 +3689,13 @@
         <v>29</v>
       </c>
       <c r="D14" t="s">
-        <v>946</v>
+        <v>915</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>957</v>
+        <v>926</v>
       </c>
       <c r="G14" t="s">
         <v>11</v>
@@ -3681,13 +3712,13 @@
         <v>31</v>
       </c>
       <c r="D15" t="s">
-        <v>947</v>
+        <v>916</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>957</v>
+        <v>926</v>
       </c>
       <c r="G15" t="s">
         <v>11</v>
@@ -3704,13 +3735,13 @@
         <v>33</v>
       </c>
       <c r="D16" t="s">
-        <v>948</v>
+        <v>917</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>957</v>
+        <v>926</v>
       </c>
       <c r="G16" t="s">
         <v>11</v>
@@ -3727,13 +3758,13 @@
         <v>35</v>
       </c>
       <c r="D17" t="s">
-        <v>949</v>
+        <v>918</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>957</v>
+        <v>926</v>
       </c>
       <c r="G17" t="s">
         <v>11</v>
@@ -3750,13 +3781,13 @@
         <v>37</v>
       </c>
       <c r="D18" t="s">
-        <v>950</v>
+        <v>919</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>957</v>
+        <v>926</v>
       </c>
       <c r="G18" t="s">
         <v>11</v>
@@ -3767,19 +3798,19 @@
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="C19" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="D19" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="E19" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>957</v>
+        <v>926</v>
       </c>
       <c r="G19" t="s">
         <v>11</v>
@@ -3796,13 +3827,13 @@
         <v>39</v>
       </c>
       <c r="D20" t="s">
-        <v>924</v>
+        <v>893</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>957</v>
+        <v>926</v>
       </c>
       <c r="G20" t="s">
         <v>11</v>
@@ -3819,13 +3850,13 @@
         <v>41</v>
       </c>
       <c r="D21" t="s">
-        <v>951</v>
+        <v>920</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>957</v>
+        <v>926</v>
       </c>
       <c r="G21" t="s">
         <v>11</v>
@@ -3842,13 +3873,13 @@
         <v>43</v>
       </c>
       <c r="D22" t="s">
-        <v>952</v>
+        <v>921</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>957</v>
+        <v>926</v>
       </c>
       <c r="G22" t="s">
         <v>11</v>
@@ -3865,13 +3896,13 @@
         <v>45</v>
       </c>
       <c r="D23" t="s">
-        <v>955</v>
+        <v>924</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>957</v>
+        <v>926</v>
       </c>
       <c r="G23" t="s">
         <v>11</v>
@@ -3888,13 +3919,13 @@
         <v>47</v>
       </c>
       <c r="D24" t="s">
-        <v>954</v>
+        <v>923</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>957</v>
+        <v>926</v>
       </c>
       <c r="G24" t="s">
         <v>11</v>
@@ -3911,13 +3942,13 @@
         <v>49</v>
       </c>
       <c r="D25" t="s">
-        <v>956</v>
+        <v>925</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>957</v>
+        <v>926</v>
       </c>
       <c r="G25" t="s">
         <v>11</v>
@@ -3939,6 +3970,9 @@
       <c r="E26" t="s">
         <v>9</v>
       </c>
+      <c r="F26" s="1" t="s">
+        <v>926</v>
+      </c>
       <c r="G26" t="s">
         <v>11</v>
       </c>
@@ -3954,10 +3988,13 @@
         <v>54</v>
       </c>
       <c r="D27" t="s">
-        <v>925</v>
+        <v>894</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G27" t="s">
         <v>11</v>
@@ -3979,6 +4016,9 @@
       <c r="E28" t="s">
         <v>9</v>
       </c>
+      <c r="F28" s="1" t="s">
+        <v>926</v>
+      </c>
       <c r="G28" t="s">
         <v>11</v>
       </c>
@@ -3994,10 +4034,13 @@
         <v>59</v>
       </c>
       <c r="D29" t="s">
-        <v>927</v>
+        <v>896</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G29" t="s">
         <v>11</v>
@@ -4014,10 +4057,13 @@
         <v>61</v>
       </c>
       <c r="D30" t="s">
-        <v>62</v>
+        <v>928</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G30" t="s">
         <v>11</v>
@@ -4028,16 +4074,19 @@
         <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C31" t="s">
+        <v>895</v>
+      </c>
+      <c r="D31" t="s">
+        <v>897</v>
+      </c>
+      <c r="E31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>926</v>
-      </c>
-      <c r="D31" t="s">
-        <v>928</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
       </c>
       <c r="G31" t="s">
         <v>11</v>
@@ -4048,16 +4097,19 @@
         <v>28</v>
       </c>
       <c r="B32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" t="s">
         <v>64</v>
       </c>
-      <c r="C32" t="s">
-        <v>65</v>
-      </c>
       <c r="D32" t="s">
-        <v>66</v>
+        <v>929</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G32" t="s">
         <v>11</v>
@@ -4068,16 +4120,19 @@
         <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C33" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D33" t="s">
-        <v>69</v>
+        <v>930</v>
       </c>
       <c r="E33" t="s">
         <v>9</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G33" t="s">
         <v>11</v>
@@ -4088,16 +4143,19 @@
         <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C34" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D34" t="s">
-        <v>72</v>
+        <v>931</v>
       </c>
       <c r="E34" t="s">
         <v>9</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G34" t="s">
         <v>11</v>
@@ -4108,16 +4166,19 @@
         <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C35" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D35" t="s">
-        <v>930</v>
+        <v>899</v>
       </c>
       <c r="E35" t="s">
         <v>9</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G35" t="s">
         <v>11</v>
@@ -4128,16 +4189,19 @@
         <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C36" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D36" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E36" t="s">
         <v>9</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G36" t="s">
         <v>11</v>
@@ -4148,16 +4212,19 @@
         <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D37" t="s">
-        <v>80</v>
+        <v>932</v>
       </c>
       <c r="E37" t="s">
         <v>9</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G37" t="s">
         <v>11</v>
@@ -4168,16 +4235,19 @@
         <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C38" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D38" t="s">
-        <v>929</v>
+        <v>898</v>
       </c>
       <c r="E38" t="s">
         <v>9</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G38" t="s">
         <v>11</v>
@@ -4188,16 +4258,19 @@
         <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C39" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D39" t="s">
-        <v>931</v>
+        <v>900</v>
       </c>
       <c r="E39" t="s">
         <v>9</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G39" t="s">
         <v>11</v>
@@ -4208,16 +4281,19 @@
         <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C40" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D40" t="s">
-        <v>932</v>
+        <v>901</v>
       </c>
       <c r="E40" t="s">
         <v>9</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G40" t="s">
         <v>11</v>
@@ -4228,16 +4304,19 @@
         <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C41" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D41" t="s">
-        <v>933</v>
+        <v>902</v>
       </c>
       <c r="E41" t="s">
         <v>9</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G41" t="s">
         <v>11</v>
@@ -4248,16 +4327,19 @@
         <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C42" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D42" t="s">
-        <v>91</v>
+        <v>933</v>
       </c>
       <c r="E42" t="s">
         <v>9</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G42" t="s">
         <v>11</v>
@@ -4268,16 +4350,19 @@
         <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C43" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D43" t="s">
-        <v>94</v>
+        <v>934</v>
       </c>
       <c r="E43" t="s">
         <v>9</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G43" t="s">
         <v>11</v>
@@ -4288,16 +4373,19 @@
         <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C44" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="D44" t="s">
-        <v>97</v>
+        <v>935</v>
       </c>
       <c r="E44" t="s">
         <v>9</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G44" t="s">
         <v>11</v>
@@ -4308,16 +4396,19 @@
         <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C45" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D45" t="s">
-        <v>934</v>
+        <v>903</v>
       </c>
       <c r="E45" t="s">
         <v>9</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G45" t="s">
         <v>11</v>
@@ -4328,16 +4419,19 @@
         <v>42</v>
       </c>
       <c r="B46" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C46" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D46" t="s">
-        <v>102</v>
+        <v>936</v>
       </c>
       <c r="E46" t="s">
         <v>9</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G46" t="s">
         <v>11</v>
@@ -4348,16 +4442,19 @@
         <v>43</v>
       </c>
       <c r="B47" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C47" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D47" t="s">
-        <v>935</v>
+        <v>904</v>
       </c>
       <c r="E47" t="s">
         <v>9</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G47" t="s">
         <v>11</v>
@@ -4368,16 +4465,19 @@
         <v>44</v>
       </c>
       <c r="B48" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C48" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D48" t="s">
-        <v>936</v>
+        <v>905</v>
       </c>
       <c r="E48" t="s">
         <v>9</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G48" t="s">
         <v>11</v>
@@ -4388,16 +4488,19 @@
         <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="C49" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D49" t="s">
-        <v>937</v>
+        <v>906</v>
       </c>
       <c r="E49" t="s">
         <v>9</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G49" t="s">
         <v>11</v>
@@ -4408,16 +4511,19 @@
         <v>66</v>
       </c>
       <c r="B50" t="s">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="C50" t="s">
-        <v>170</v>
+        <v>141</v>
       </c>
       <c r="D50" t="s">
-        <v>171</v>
+        <v>937</v>
       </c>
       <c r="E50" t="s">
         <v>9</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G50" t="s">
         <v>11</v>
@@ -4428,16 +4534,19 @@
         <v>46</v>
       </c>
       <c r="B51" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="C51" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D51" t="s">
-        <v>111</v>
+        <v>938</v>
       </c>
       <c r="E51" t="s">
         <v>9</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G51" t="s">
         <v>11</v>
@@ -4448,16 +4557,19 @@
         <v>47</v>
       </c>
       <c r="B52" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C52" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="D52" t="s">
-        <v>114</v>
+        <v>939</v>
       </c>
       <c r="E52" t="s">
         <v>9</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G52" t="s">
         <v>11</v>
@@ -4468,16 +4580,19 @@
         <v>48</v>
       </c>
       <c r="B53" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="C53" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="D53" t="s">
-        <v>117</v>
+        <v>940</v>
       </c>
       <c r="E53" t="s">
         <v>9</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G53" t="s">
         <v>11</v>
@@ -4488,16 +4603,19 @@
         <v>49</v>
       </c>
       <c r="B54" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="C54" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="D54" t="s">
-        <v>120</v>
+        <v>941</v>
       </c>
       <c r="E54" t="s">
         <v>9</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G54" t="s">
         <v>11</v>
@@ -4508,16 +4626,19 @@
         <v>50</v>
       </c>
       <c r="B55" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="C55" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="D55" t="s">
-        <v>123</v>
+        <v>942</v>
       </c>
       <c r="E55" t="s">
         <v>9</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G55" t="s">
         <v>11</v>
@@ -4528,16 +4649,19 @@
         <v>51</v>
       </c>
       <c r="B56" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="C56" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="D56" t="s">
-        <v>126</v>
+        <v>943</v>
       </c>
       <c r="E56" t="s">
         <v>9</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G56" t="s">
         <v>11</v>
@@ -4548,16 +4672,19 @@
         <v>69</v>
       </c>
       <c r="B57" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="C57" t="s">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="D57" t="s">
-        <v>177</v>
+        <v>944</v>
       </c>
       <c r="E57" t="s">
         <v>9</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G57" t="s">
         <v>11</v>
@@ -4568,16 +4695,19 @@
         <v>52</v>
       </c>
       <c r="B58" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C58" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="D58" t="s">
-        <v>129</v>
+        <v>945</v>
       </c>
       <c r="E58" t="s">
         <v>9</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G58" t="s">
         <v>11</v>
@@ -4588,16 +4718,19 @@
         <v>53</v>
       </c>
       <c r="B59" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="C59" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="D59" t="s">
-        <v>132</v>
+        <v>946</v>
       </c>
       <c r="E59" t="s">
         <v>9</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G59" t="s">
         <v>11</v>
@@ -4608,16 +4741,19 @@
         <v>54</v>
       </c>
       <c r="B60" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="C60" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="D60" t="s">
-        <v>135</v>
+        <v>947</v>
       </c>
       <c r="E60" t="s">
         <v>9</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G60" t="s">
         <v>11</v>
@@ -4628,16 +4764,19 @@
         <v>55</v>
       </c>
       <c r="B61" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="C61" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D61" t="s">
-        <v>138</v>
+        <v>948</v>
       </c>
       <c r="E61" t="s">
         <v>9</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G61" t="s">
         <v>11</v>
@@ -4648,16 +4787,19 @@
         <v>56</v>
       </c>
       <c r="B62" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="C62" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="D62" t="s">
-        <v>141</v>
+        <v>949</v>
       </c>
       <c r="E62" t="s">
         <v>9</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G62" t="s">
         <v>11</v>
@@ -4668,16 +4810,19 @@
         <v>57</v>
       </c>
       <c r="B63" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="C63" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="D63" t="s">
-        <v>144</v>
+        <v>950</v>
       </c>
       <c r="E63" t="s">
         <v>9</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G63" t="s">
         <v>11</v>
@@ -4688,16 +4833,19 @@
         <v>58</v>
       </c>
       <c r="B64" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="C64" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="D64" t="s">
-        <v>147</v>
+        <v>951</v>
       </c>
       <c r="E64" t="s">
         <v>9</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G64" t="s">
         <v>11</v>
@@ -4708,16 +4856,19 @@
         <v>59</v>
       </c>
       <c r="B65" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="C65" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="D65" t="s">
-        <v>150</v>
+        <v>952</v>
       </c>
       <c r="E65" t="s">
         <v>9</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G65" t="s">
         <v>11</v>
@@ -4728,16 +4879,19 @@
         <v>60</v>
       </c>
       <c r="B66" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="C66" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="D66" t="s">
-        <v>153</v>
+        <v>953</v>
       </c>
       <c r="E66" t="s">
         <v>9</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G66" t="s">
         <v>11</v>
@@ -4748,16 +4902,16 @@
         <v>3</v>
       </c>
       <c r="B67" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="C67" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="D67" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="E67" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="G67" t="s">
         <v>11</v>
@@ -4768,16 +4922,16 @@
         <v>5</v>
       </c>
       <c r="B68" t="s">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="C68" t="s">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="D68" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="E68" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="G68" t="s">
         <v>11</v>
@@ -4788,16 +4942,19 @@
         <v>61</v>
       </c>
       <c r="B69" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="C69" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="D69" t="s">
-        <v>156</v>
+        <v>954</v>
       </c>
       <c r="E69" t="s">
         <v>9</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G69" t="s">
         <v>11</v>
@@ -4808,16 +4965,19 @@
         <v>62</v>
       </c>
       <c r="B70" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="C70" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="D70" t="s">
-        <v>159</v>
+        <v>955</v>
       </c>
       <c r="E70" t="s">
         <v>9</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G70" t="s">
         <v>11</v>
@@ -4828,16 +4988,16 @@
         <v>2</v>
       </c>
       <c r="B71" t="s">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="C71" t="s">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="D71" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="E71" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="G71" t="s">
         <v>11</v>
@@ -4848,16 +5008,19 @@
         <v>63</v>
       </c>
       <c r="B72" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="C72" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
       <c r="D72" t="s">
-        <v>162</v>
+        <v>956</v>
       </c>
       <c r="E72" t="s">
         <v>9</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G72" t="s">
         <v>11</v>
@@ -4868,16 +5031,19 @@
         <v>64</v>
       </c>
       <c r="B73" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="C73" t="s">
-        <v>164</v>
+        <v>137</v>
       </c>
       <c r="D73" t="s">
-        <v>165</v>
+        <v>957</v>
       </c>
       <c r="E73" t="s">
         <v>9</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G73" t="s">
         <v>11</v>
@@ -4888,16 +5054,16 @@
         <v>4</v>
       </c>
       <c r="B74" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="C74" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="D74" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="E74" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="G74" t="s">
         <v>11</v>
@@ -4908,16 +5074,19 @@
         <v>65</v>
       </c>
       <c r="B75" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="C75" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="D75" t="s">
-        <v>168</v>
+        <v>958</v>
       </c>
       <c r="E75" t="s">
         <v>9</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="G75" t="s">
         <v>11</v>
@@ -4925,7 +5094,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.15">
       <c r="C76" t="s">
-        <v>953</v>
+        <v>922</v>
       </c>
     </row>
   </sheetData>
@@ -4946,10 +5115,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G124"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>927</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -4975,18 +5153,18 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>189</v>
+        <v>158</v>
       </c>
       <c r="C2" t="s">
-        <v>190</v>
+        <v>159</v>
       </c>
       <c r="D2" t="s">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G2" t="s">
@@ -4998,18 +5176,18 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="C3" t="s">
-        <v>193</v>
+        <v>162</v>
       </c>
       <c r="D3" t="s">
-        <v>194</v>
+        <v>163</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G3" t="s">
@@ -5021,18 +5199,18 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="C4" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="D4" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G4" t="s">
@@ -5044,18 +5222,18 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>198</v>
+        <v>167</v>
       </c>
       <c r="C5" t="s">
-        <v>199</v>
+        <v>168</v>
       </c>
       <c r="D5" t="s">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G5" t="s">
@@ -5067,18 +5245,18 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="C6" t="s">
-        <v>202</v>
+        <v>171</v>
       </c>
       <c r="D6" t="s">
-        <v>203</v>
+        <v>172</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G6" t="s">
@@ -5090,18 +5268,18 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>204</v>
+        <v>173</v>
       </c>
       <c r="C7" t="s">
-        <v>205</v>
+        <v>174</v>
       </c>
       <c r="D7" t="s">
-        <v>206</v>
+        <v>175</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G7" t="s">
@@ -5113,18 +5291,18 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>207</v>
+        <v>176</v>
       </c>
       <c r="C8" t="s">
-        <v>208</v>
+        <v>177</v>
       </c>
       <c r="D8" t="s">
-        <v>209</v>
+        <v>178</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G8" t="s">
@@ -5136,18 +5314,18 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="C9" t="s">
-        <v>211</v>
+        <v>180</v>
       </c>
       <c r="D9" t="s">
-        <v>212</v>
+        <v>181</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G9" t="s">
@@ -5159,18 +5337,18 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>213</v>
+        <v>182</v>
       </c>
       <c r="C10" t="s">
-        <v>214</v>
+        <v>183</v>
       </c>
       <c r="D10" t="s">
-        <v>215</v>
+        <v>184</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G10" t="s">
@@ -5182,18 +5360,18 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="C11" t="s">
-        <v>217</v>
+        <v>186</v>
       </c>
       <c r="D11" t="s">
-        <v>218</v>
+        <v>187</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G11" t="s">
@@ -5205,18 +5383,18 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>219</v>
+        <v>188</v>
       </c>
       <c r="C12" t="s">
-        <v>220</v>
+        <v>189</v>
       </c>
       <c r="D12" t="s">
-        <v>221</v>
+        <v>190</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G12" t="s">
@@ -5228,18 +5406,18 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>222</v>
+        <v>191</v>
       </c>
       <c r="C13" t="s">
-        <v>223</v>
+        <v>192</v>
       </c>
       <c r="D13" t="s">
-        <v>224</v>
+        <v>193</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G13" t="s">
@@ -5251,18 +5429,18 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>225</v>
+        <v>194</v>
       </c>
       <c r="C14" t="s">
-        <v>226</v>
+        <v>195</v>
       </c>
       <c r="D14" t="s">
-        <v>227</v>
+        <v>196</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G14" t="s">
@@ -5274,18 +5452,18 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>228</v>
+        <v>197</v>
       </c>
       <c r="C15" t="s">
-        <v>229</v>
+        <v>198</v>
       </c>
       <c r="D15" t="s">
-        <v>230</v>
+        <v>199</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G15" t="s">
@@ -5297,18 +5475,18 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>231</v>
+        <v>200</v>
       </c>
       <c r="C16" t="s">
-        <v>232</v>
+        <v>201</v>
       </c>
       <c r="D16" t="s">
-        <v>233</v>
+        <v>202</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G16" t="s">
@@ -5320,18 +5498,18 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>234</v>
+        <v>203</v>
       </c>
       <c r="C17" t="s">
-        <v>235</v>
+        <v>204</v>
       </c>
       <c r="D17" t="s">
-        <v>236</v>
+        <v>205</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G17" t="s">
@@ -5343,18 +5521,18 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>237</v>
+        <v>206</v>
       </c>
       <c r="C18" t="s">
-        <v>238</v>
+        <v>207</v>
       </c>
       <c r="D18" t="s">
-        <v>239</v>
+        <v>208</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G18" t="s">
@@ -5366,18 +5544,18 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>240</v>
+        <v>209</v>
       </c>
       <c r="C19" t="s">
-        <v>241</v>
+        <v>210</v>
       </c>
       <c r="D19" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G19" t="s">
@@ -5389,18 +5567,18 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>243</v>
+        <v>212</v>
       </c>
       <c r="C20" t="s">
-        <v>244</v>
+        <v>213</v>
       </c>
       <c r="D20" t="s">
-        <v>245</v>
+        <v>214</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G20" t="s">
@@ -5412,18 +5590,18 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>246</v>
+        <v>215</v>
       </c>
       <c r="C21" t="s">
-        <v>247</v>
+        <v>216</v>
       </c>
       <c r="D21" t="s">
-        <v>248</v>
+        <v>217</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G21" t="s">
@@ -5435,18 +5613,18 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>249</v>
+        <v>218</v>
       </c>
       <c r="C22" t="s">
-        <v>250</v>
+        <v>219</v>
       </c>
       <c r="D22" t="s">
-        <v>251</v>
+        <v>220</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G22" t="s">
@@ -5458,18 +5636,18 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="C23" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="D23" t="s">
-        <v>254</v>
+        <v>223</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G23" t="s">
@@ -5481,18 +5659,18 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>255</v>
+        <v>224</v>
       </c>
       <c r="C24" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="D24" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G24" t="s">
@@ -5504,18 +5682,18 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>258</v>
+        <v>227</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>228</v>
       </c>
       <c r="D25" t="s">
-        <v>260</v>
+        <v>229</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G25" t="s">
@@ -5527,18 +5705,18 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>261</v>
+        <v>230</v>
       </c>
       <c r="C26" t="s">
-        <v>262</v>
+        <v>231</v>
       </c>
       <c r="D26" t="s">
-        <v>263</v>
+        <v>232</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G26" t="s">
@@ -5550,18 +5728,18 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>264</v>
+        <v>233</v>
       </c>
       <c r="C27" t="s">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="D27" t="s">
-        <v>266</v>
+        <v>235</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G27" t="s">
@@ -5573,18 +5751,18 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>267</v>
+        <v>236</v>
       </c>
       <c r="C28" t="s">
-        <v>268</v>
+        <v>237</v>
       </c>
       <c r="D28" t="s">
-        <v>269</v>
+        <v>238</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G28" t="s">
@@ -5596,18 +5774,18 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>270</v>
+        <v>239</v>
       </c>
       <c r="C29" t="s">
-        <v>271</v>
+        <v>240</v>
       </c>
       <c r="D29" t="s">
-        <v>272</v>
+        <v>241</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G29" t="s">
@@ -5619,18 +5797,18 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>273</v>
+        <v>242</v>
       </c>
       <c r="C30" t="s">
-        <v>274</v>
+        <v>243</v>
       </c>
       <c r="D30" t="s">
-        <v>275</v>
+        <v>244</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G30" t="s">
@@ -5642,18 +5820,18 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>276</v>
+        <v>245</v>
       </c>
       <c r="C31" t="s">
-        <v>277</v>
+        <v>246</v>
       </c>
       <c r="D31" t="s">
-        <v>278</v>
+        <v>247</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G31" t="s">
@@ -5665,18 +5843,18 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>279</v>
+        <v>248</v>
       </c>
       <c r="C32" t="s">
-        <v>280</v>
+        <v>249</v>
       </c>
       <c r="D32" t="s">
-        <v>281</v>
+        <v>250</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G32" t="s">
@@ -5688,18 +5866,18 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>282</v>
+        <v>251</v>
       </c>
       <c r="C33" t="s">
-        <v>283</v>
+        <v>252</v>
       </c>
       <c r="D33" t="s">
-        <v>284</v>
+        <v>253</v>
       </c>
       <c r="E33" t="s">
         <v>9</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G33" t="s">
@@ -5711,18 +5889,18 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>285</v>
+        <v>254</v>
       </c>
       <c r="C34" t="s">
-        <v>286</v>
+        <v>255</v>
       </c>
       <c r="D34" t="s">
-        <v>287</v>
+        <v>256</v>
       </c>
       <c r="E34" t="s">
         <v>9</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F34" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G34" t="s">
@@ -5734,18 +5912,18 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>288</v>
+        <v>257</v>
       </c>
       <c r="C35" t="s">
-        <v>289</v>
+        <v>258</v>
       </c>
       <c r="D35" t="s">
-        <v>290</v>
+        <v>259</v>
       </c>
       <c r="E35" t="s">
         <v>9</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G35" t="s">
@@ -5757,18 +5935,18 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>291</v>
+        <v>260</v>
       </c>
       <c r="C36" t="s">
-        <v>292</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>293</v>
+        <v>262</v>
       </c>
       <c r="E36" t="s">
         <v>9</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G36" t="s">
@@ -5780,18 +5958,18 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>294</v>
+        <v>263</v>
       </c>
       <c r="C37" t="s">
-        <v>295</v>
+        <v>264</v>
       </c>
       <c r="D37" t="s">
-        <v>296</v>
+        <v>265</v>
       </c>
       <c r="E37" t="s">
         <v>9</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G37" t="s">
@@ -5803,18 +5981,18 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>297</v>
+        <v>266</v>
       </c>
       <c r="C38" t="s">
-        <v>298</v>
+        <v>267</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>268</v>
       </c>
       <c r="E38" t="s">
         <v>9</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F38" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G38" t="s">
@@ -5826,18 +6004,18 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>300</v>
+        <v>269</v>
       </c>
       <c r="C39" t="s">
-        <v>301</v>
+        <v>270</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>271</v>
       </c>
       <c r="E39" t="s">
         <v>9</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F39" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G39" t="s">
@@ -5849,18 +6027,18 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>303</v>
+        <v>272</v>
       </c>
       <c r="C40" t="s">
-        <v>304</v>
+        <v>273</v>
       </c>
       <c r="D40" t="s">
-        <v>305</v>
+        <v>274</v>
       </c>
       <c r="E40" t="s">
         <v>9</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G40" t="s">
@@ -5872,18 +6050,18 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>306</v>
+        <v>275</v>
       </c>
       <c r="C41" t="s">
-        <v>307</v>
+        <v>276</v>
       </c>
       <c r="D41" t="s">
-        <v>308</v>
+        <v>277</v>
       </c>
       <c r="E41" t="s">
         <v>9</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F41" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G41" t="s">
@@ -5895,18 +6073,18 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>309</v>
+        <v>278</v>
       </c>
       <c r="C42" t="s">
-        <v>310</v>
+        <v>279</v>
       </c>
       <c r="D42" t="s">
-        <v>311</v>
+        <v>280</v>
       </c>
       <c r="E42" t="s">
         <v>9</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F42" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G42" t="s">
@@ -5918,18 +6096,18 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>312</v>
+        <v>281</v>
       </c>
       <c r="C43" t="s">
-        <v>313</v>
+        <v>282</v>
       </c>
       <c r="D43" t="s">
-        <v>314</v>
+        <v>283</v>
       </c>
       <c r="E43" t="s">
         <v>9</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F43" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G43" t="s">
@@ -5941,18 +6119,18 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>315</v>
+        <v>284</v>
       </c>
       <c r="C44" t="s">
-        <v>316</v>
+        <v>285</v>
       </c>
       <c r="D44" t="s">
-        <v>317</v>
+        <v>286</v>
       </c>
       <c r="E44" t="s">
         <v>9</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F44" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G44" t="s">
@@ -5964,18 +6142,18 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>318</v>
+        <v>287</v>
       </c>
       <c r="C45" t="s">
-        <v>319</v>
+        <v>288</v>
       </c>
       <c r="D45" t="s">
-        <v>320</v>
+        <v>289</v>
       </c>
       <c r="E45" t="s">
         <v>9</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F45" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G45" t="s">
@@ -5987,18 +6165,18 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>321</v>
+        <v>290</v>
       </c>
       <c r="C46" t="s">
-        <v>322</v>
+        <v>291</v>
       </c>
       <c r="D46" t="s">
-        <v>323</v>
+        <v>292</v>
       </c>
       <c r="E46" t="s">
         <v>9</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F46" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G46" t="s">
@@ -6010,18 +6188,18 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>324</v>
+        <v>293</v>
       </c>
       <c r="C47" t="s">
-        <v>325</v>
+        <v>294</v>
       </c>
       <c r="D47" t="s">
-        <v>326</v>
+        <v>295</v>
       </c>
       <c r="E47" t="s">
         <v>9</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F47" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G47" t="s">
@@ -6033,18 +6211,18 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>327</v>
+        <v>296</v>
       </c>
       <c r="C48" t="s">
-        <v>328</v>
+        <v>297</v>
       </c>
       <c r="D48" t="s">
-        <v>329</v>
+        <v>298</v>
       </c>
       <c r="E48" t="s">
         <v>9</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F48" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G48" t="s">
@@ -6056,18 +6234,18 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>330</v>
+        <v>299</v>
       </c>
       <c r="C49" t="s">
-        <v>331</v>
+        <v>300</v>
       </c>
       <c r="D49" t="s">
-        <v>332</v>
+        <v>301</v>
       </c>
       <c r="E49" t="s">
         <v>9</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F49" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G49" t="s">
@@ -6079,18 +6257,18 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>333</v>
+        <v>302</v>
       </c>
       <c r="C50" t="s">
-        <v>334</v>
+        <v>303</v>
       </c>
       <c r="D50" t="s">
-        <v>335</v>
+        <v>304</v>
       </c>
       <c r="E50" t="s">
         <v>9</v>
       </c>
-      <c r="F50" t="s">
+      <c r="F50" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G50" t="s">
@@ -6102,18 +6280,18 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>336</v>
+        <v>305</v>
       </c>
       <c r="C51" t="s">
-        <v>337</v>
+        <v>306</v>
       </c>
       <c r="D51" t="s">
-        <v>338</v>
+        <v>307</v>
       </c>
       <c r="E51" t="s">
         <v>9</v>
       </c>
-      <c r="F51" t="s">
+      <c r="F51" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G51" t="s">
@@ -6125,18 +6303,18 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>339</v>
+        <v>308</v>
       </c>
       <c r="C52" t="s">
-        <v>340</v>
+        <v>309</v>
       </c>
       <c r="D52" t="s">
-        <v>341</v>
+        <v>310</v>
       </c>
       <c r="E52" t="s">
         <v>9</v>
       </c>
-      <c r="F52" t="s">
+      <c r="F52" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G52" t="s">
@@ -6148,18 +6326,18 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>342</v>
+        <v>311</v>
       </c>
       <c r="C53" t="s">
-        <v>343</v>
+        <v>312</v>
       </c>
       <c r="D53" t="s">
-        <v>344</v>
+        <v>313</v>
       </c>
       <c r="E53" t="s">
         <v>9</v>
       </c>
-      <c r="F53" t="s">
+      <c r="F53" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G53" t="s">
@@ -6171,18 +6349,18 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>345</v>
+        <v>314</v>
       </c>
       <c r="C54" t="s">
-        <v>346</v>
+        <v>315</v>
       </c>
       <c r="D54" t="s">
-        <v>347</v>
+        <v>316</v>
       </c>
       <c r="E54" t="s">
         <v>9</v>
       </c>
-      <c r="F54" t="s">
+      <c r="F54" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G54" t="s">
@@ -6194,18 +6372,18 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>348</v>
+        <v>317</v>
       </c>
       <c r="C55" t="s">
-        <v>349</v>
+        <v>318</v>
       </c>
       <c r="D55" t="s">
-        <v>350</v>
+        <v>319</v>
       </c>
       <c r="E55" t="s">
         <v>9</v>
       </c>
-      <c r="F55" t="s">
+      <c r="F55" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G55" t="s">
@@ -6217,18 +6395,18 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>351</v>
+        <v>320</v>
       </c>
       <c r="C56" t="s">
-        <v>352</v>
+        <v>321</v>
       </c>
       <c r="D56" t="s">
-        <v>353</v>
+        <v>322</v>
       </c>
       <c r="E56" t="s">
         <v>9</v>
       </c>
-      <c r="F56" t="s">
+      <c r="F56" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G56" t="s">
@@ -6240,18 +6418,18 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>354</v>
+        <v>323</v>
       </c>
       <c r="C57" t="s">
-        <v>355</v>
+        <v>324</v>
       </c>
       <c r="D57" t="s">
-        <v>356</v>
+        <v>325</v>
       </c>
       <c r="E57" t="s">
         <v>9</v>
       </c>
-      <c r="F57" t="s">
+      <c r="F57" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G57" t="s">
@@ -6263,18 +6441,18 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>357</v>
+        <v>326</v>
       </c>
       <c r="C58" t="s">
-        <v>358</v>
+        <v>327</v>
       </c>
       <c r="D58" t="s">
-        <v>359</v>
+        <v>328</v>
       </c>
       <c r="E58" t="s">
         <v>9</v>
       </c>
-      <c r="F58" t="s">
+      <c r="F58" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G58" t="s">
@@ -6286,18 +6464,18 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>360</v>
+        <v>329</v>
       </c>
       <c r="C59" t="s">
-        <v>361</v>
+        <v>330</v>
       </c>
       <c r="D59" t="s">
-        <v>362</v>
+        <v>331</v>
       </c>
       <c r="E59" t="s">
         <v>9</v>
       </c>
-      <c r="F59" t="s">
+      <c r="F59" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G59" t="s">
@@ -6309,18 +6487,18 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>363</v>
+        <v>332</v>
       </c>
       <c r="C60" t="s">
-        <v>364</v>
+        <v>333</v>
       </c>
       <c r="D60" t="s">
-        <v>365</v>
+        <v>334</v>
       </c>
       <c r="E60" t="s">
         <v>9</v>
       </c>
-      <c r="F60" t="s">
+      <c r="F60" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G60" t="s">
@@ -6332,18 +6510,18 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>366</v>
+        <v>335</v>
       </c>
       <c r="C61" t="s">
-        <v>367</v>
+        <v>336</v>
       </c>
       <c r="D61" t="s">
-        <v>368</v>
+        <v>337</v>
       </c>
       <c r="E61" t="s">
         <v>9</v>
       </c>
-      <c r="F61" t="s">
+      <c r="F61" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G61" t="s">
@@ -6355,18 +6533,18 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>369</v>
+        <v>338</v>
       </c>
       <c r="C62" t="s">
-        <v>370</v>
+        <v>339</v>
       </c>
       <c r="D62" t="s">
-        <v>371</v>
+        <v>340</v>
       </c>
       <c r="E62" t="s">
         <v>9</v>
       </c>
-      <c r="F62" t="s">
+      <c r="F62" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G62" t="s">
@@ -6378,18 +6556,18 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>372</v>
+        <v>341</v>
       </c>
       <c r="C63" t="s">
-        <v>373</v>
+        <v>342</v>
       </c>
       <c r="D63" t="s">
-        <v>374</v>
+        <v>343</v>
       </c>
       <c r="E63" t="s">
         <v>9</v>
       </c>
-      <c r="F63" t="s">
+      <c r="F63" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G63" t="s">
@@ -6401,18 +6579,18 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>375</v>
+        <v>344</v>
       </c>
       <c r="C64" t="s">
-        <v>376</v>
+        <v>345</v>
       </c>
       <c r="D64" t="s">
-        <v>377</v>
+        <v>346</v>
       </c>
       <c r="E64" t="s">
         <v>9</v>
       </c>
-      <c r="F64" t="s">
+      <c r="F64" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G64" t="s">
@@ -6424,18 +6602,18 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>378</v>
+        <v>347</v>
       </c>
       <c r="C65" t="s">
-        <v>379</v>
+        <v>348</v>
       </c>
       <c r="D65" t="s">
-        <v>380</v>
+        <v>349</v>
       </c>
       <c r="E65" t="s">
         <v>9</v>
       </c>
-      <c r="F65" t="s">
+      <c r="F65" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G65" t="s">
@@ -6447,18 +6625,18 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>381</v>
+        <v>350</v>
       </c>
       <c r="C66" t="s">
-        <v>382</v>
+        <v>351</v>
       </c>
       <c r="D66" t="s">
-        <v>383</v>
+        <v>352</v>
       </c>
       <c r="E66" t="s">
         <v>9</v>
       </c>
-      <c r="F66" t="s">
+      <c r="F66" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G66" t="s">
@@ -6470,18 +6648,18 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>384</v>
+        <v>353</v>
       </c>
       <c r="C67" t="s">
-        <v>385</v>
+        <v>354</v>
       </c>
       <c r="D67" t="s">
-        <v>386</v>
+        <v>355</v>
       </c>
       <c r="E67" t="s">
         <v>9</v>
       </c>
-      <c r="F67" t="s">
+      <c r="F67" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G67" t="s">
@@ -6493,18 +6671,18 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>387</v>
+        <v>356</v>
       </c>
       <c r="C68" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="D68" t="s">
-        <v>389</v>
+        <v>358</v>
       </c>
       <c r="E68" t="s">
         <v>9</v>
       </c>
-      <c r="F68" t="s">
+      <c r="F68" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G68" t="s">
@@ -6516,18 +6694,18 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>390</v>
+        <v>359</v>
       </c>
       <c r="C69" t="s">
-        <v>391</v>
+        <v>360</v>
       </c>
       <c r="D69" t="s">
-        <v>392</v>
+        <v>361</v>
       </c>
       <c r="E69" t="s">
         <v>9</v>
       </c>
-      <c r="F69" t="s">
+      <c r="F69" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G69" t="s">
@@ -6539,18 +6717,18 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>393</v>
+        <v>362</v>
       </c>
       <c r="C70" t="s">
-        <v>394</v>
+        <v>363</v>
       </c>
       <c r="D70" t="s">
-        <v>395</v>
+        <v>364</v>
       </c>
       <c r="E70" t="s">
         <v>9</v>
       </c>
-      <c r="F70" t="s">
+      <c r="F70" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G70" t="s">
@@ -6562,18 +6740,18 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>396</v>
+        <v>365</v>
       </c>
       <c r="C71" t="s">
-        <v>397</v>
+        <v>366</v>
       </c>
       <c r="D71" t="s">
-        <v>398</v>
+        <v>367</v>
       </c>
       <c r="E71" t="s">
         <v>9</v>
       </c>
-      <c r="F71" t="s">
+      <c r="F71" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G71" t="s">
@@ -6585,18 +6763,18 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>399</v>
+        <v>368</v>
       </c>
       <c r="C72" t="s">
-        <v>400</v>
+        <v>369</v>
       </c>
       <c r="D72" t="s">
-        <v>401</v>
+        <v>370</v>
       </c>
       <c r="E72" t="s">
         <v>9</v>
       </c>
-      <c r="F72" t="s">
+      <c r="F72" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G72" t="s">
@@ -6608,18 +6786,18 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>402</v>
+        <v>371</v>
       </c>
       <c r="C73" t="s">
-        <v>403</v>
+        <v>372</v>
       </c>
       <c r="D73" t="s">
-        <v>404</v>
+        <v>373</v>
       </c>
       <c r="E73" t="s">
         <v>9</v>
       </c>
-      <c r="F73" t="s">
+      <c r="F73" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G73" t="s">
@@ -6631,18 +6809,18 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>405</v>
+        <v>374</v>
       </c>
       <c r="C74" t="s">
-        <v>406</v>
+        <v>375</v>
       </c>
       <c r="D74" t="s">
-        <v>407</v>
+        <v>376</v>
       </c>
       <c r="E74" t="s">
         <v>9</v>
       </c>
-      <c r="F74" t="s">
+      <c r="F74" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G74" t="s">
@@ -6654,18 +6832,18 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>408</v>
+        <v>377</v>
       </c>
       <c r="C75" t="s">
-        <v>409</v>
+        <v>378</v>
       </c>
       <c r="D75" t="s">
-        <v>410</v>
+        <v>379</v>
       </c>
       <c r="E75" t="s">
         <v>9</v>
       </c>
-      <c r="F75" t="s">
+      <c r="F75" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G75" t="s">
@@ -6677,18 +6855,18 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>411</v>
+        <v>380</v>
       </c>
       <c r="C76" t="s">
-        <v>412</v>
+        <v>381</v>
       </c>
       <c r="D76" t="s">
-        <v>413</v>
+        <v>382</v>
       </c>
       <c r="E76" t="s">
         <v>9</v>
       </c>
-      <c r="F76" t="s">
+      <c r="F76" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G76" t="s">
@@ -6700,18 +6878,18 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>414</v>
+        <v>383</v>
       </c>
       <c r="C77" t="s">
-        <v>415</v>
+        <v>384</v>
       </c>
       <c r="D77" t="s">
-        <v>416</v>
+        <v>385</v>
       </c>
       <c r="E77" t="s">
         <v>9</v>
       </c>
-      <c r="F77" t="s">
+      <c r="F77" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G77" t="s">
@@ -6723,18 +6901,18 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>417</v>
+        <v>386</v>
       </c>
       <c r="C78" t="s">
-        <v>418</v>
+        <v>387</v>
       </c>
       <c r="D78" t="s">
-        <v>419</v>
+        <v>388</v>
       </c>
       <c r="E78" t="s">
         <v>9</v>
       </c>
-      <c r="F78" t="s">
+      <c r="F78" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G78" t="s">
@@ -6746,18 +6924,18 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>420</v>
+        <v>389</v>
       </c>
       <c r="C79" t="s">
-        <v>421</v>
+        <v>390</v>
       </c>
       <c r="D79" t="s">
-        <v>422</v>
+        <v>391</v>
       </c>
       <c r="E79" t="s">
         <v>9</v>
       </c>
-      <c r="F79" t="s">
+      <c r="F79" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G79" t="s">
@@ -6769,18 +6947,18 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>423</v>
+        <v>392</v>
       </c>
       <c r="C80" t="s">
-        <v>424</v>
+        <v>393</v>
       </c>
       <c r="D80" t="s">
-        <v>425</v>
+        <v>394</v>
       </c>
       <c r="E80" t="s">
         <v>9</v>
       </c>
-      <c r="F80" t="s">
+      <c r="F80" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G80" t="s">
@@ -6792,18 +6970,18 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>426</v>
+        <v>395</v>
       </c>
       <c r="C81" t="s">
-        <v>427</v>
+        <v>396</v>
       </c>
       <c r="D81" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="E81" t="s">
         <v>9</v>
       </c>
-      <c r="F81" t="s">
+      <c r="F81" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G81" t="s">
@@ -6815,18 +6993,18 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>429</v>
+        <v>398</v>
       </c>
       <c r="C82" t="s">
-        <v>430</v>
+        <v>399</v>
       </c>
       <c r="D82" t="s">
-        <v>431</v>
+        <v>400</v>
       </c>
       <c r="E82" t="s">
         <v>9</v>
       </c>
-      <c r="F82" t="s">
+      <c r="F82" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G82" t="s">
@@ -6838,18 +7016,18 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>432</v>
+        <v>401</v>
       </c>
       <c r="C83" t="s">
-        <v>433</v>
+        <v>402</v>
       </c>
       <c r="D83" t="s">
-        <v>434</v>
+        <v>403</v>
       </c>
       <c r="E83" t="s">
         <v>9</v>
       </c>
-      <c r="F83" t="s">
+      <c r="F83" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G83" t="s">
@@ -6861,18 +7039,18 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>435</v>
+        <v>404</v>
       </c>
       <c r="C84" t="s">
-        <v>436</v>
+        <v>405</v>
       </c>
       <c r="D84" t="s">
-        <v>437</v>
+        <v>406</v>
       </c>
       <c r="E84" t="s">
         <v>9</v>
       </c>
-      <c r="F84" t="s">
+      <c r="F84" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G84" t="s">
@@ -6884,18 +7062,18 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>438</v>
+        <v>407</v>
       </c>
       <c r="C85" t="s">
-        <v>439</v>
+        <v>408</v>
       </c>
       <c r="D85" t="s">
-        <v>440</v>
+        <v>409</v>
       </c>
       <c r="E85" t="s">
         <v>9</v>
       </c>
-      <c r="F85" t="s">
+      <c r="F85" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G85" t="s">
@@ -6907,18 +7085,18 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>441</v>
+        <v>410</v>
       </c>
       <c r="C86" t="s">
-        <v>442</v>
+        <v>411</v>
       </c>
       <c r="D86" t="s">
-        <v>443</v>
+        <v>412</v>
       </c>
       <c r="E86" t="s">
         <v>9</v>
       </c>
-      <c r="F86" t="s">
+      <c r="F86" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G86" t="s">
@@ -6930,18 +7108,18 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>444</v>
+        <v>413</v>
       </c>
       <c r="C87" t="s">
-        <v>445</v>
+        <v>414</v>
       </c>
       <c r="D87" t="s">
-        <v>446</v>
+        <v>415</v>
       </c>
       <c r="E87" t="s">
         <v>9</v>
       </c>
-      <c r="F87" t="s">
+      <c r="F87" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G87" t="s">
@@ -6953,18 +7131,18 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>447</v>
+        <v>416</v>
       </c>
       <c r="C88" t="s">
-        <v>448</v>
+        <v>417</v>
       </c>
       <c r="D88" t="s">
-        <v>449</v>
+        <v>418</v>
       </c>
       <c r="E88" t="s">
         <v>9</v>
       </c>
-      <c r="F88" t="s">
+      <c r="F88" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G88" t="s">
@@ -6976,18 +7154,18 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>450</v>
+        <v>419</v>
       </c>
       <c r="C89" t="s">
-        <v>451</v>
+        <v>420</v>
       </c>
       <c r="D89" t="s">
-        <v>452</v>
+        <v>421</v>
       </c>
       <c r="E89" t="s">
         <v>9</v>
       </c>
-      <c r="F89" t="s">
+      <c r="F89" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G89" t="s">
@@ -6999,18 +7177,18 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>453</v>
+        <v>422</v>
       </c>
       <c r="C90" t="s">
-        <v>454</v>
+        <v>423</v>
       </c>
       <c r="D90" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="E90" t="s">
         <v>9</v>
       </c>
-      <c r="F90" t="s">
+      <c r="F90" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G90" t="s">
@@ -7022,18 +7200,18 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>456</v>
+        <v>425</v>
       </c>
       <c r="C91" t="s">
-        <v>457</v>
+        <v>426</v>
       </c>
       <c r="D91" t="s">
-        <v>458</v>
+        <v>427</v>
       </c>
       <c r="E91" t="s">
         <v>9</v>
       </c>
-      <c r="F91" t="s">
+      <c r="F91" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G91" t="s">
@@ -7045,18 +7223,18 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>459</v>
+        <v>428</v>
       </c>
       <c r="C92" t="s">
-        <v>460</v>
+        <v>429</v>
       </c>
       <c r="D92" t="s">
-        <v>461</v>
+        <v>430</v>
       </c>
       <c r="E92" t="s">
         <v>9</v>
       </c>
-      <c r="F92" t="s">
+      <c r="F92" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G92" t="s">
@@ -7068,18 +7246,18 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>462</v>
+        <v>431</v>
       </c>
       <c r="C93" t="s">
-        <v>463</v>
+        <v>432</v>
       </c>
       <c r="D93" t="s">
-        <v>464</v>
+        <v>433</v>
       </c>
       <c r="E93" t="s">
         <v>9</v>
       </c>
-      <c r="F93" t="s">
+      <c r="F93" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G93" t="s">
@@ -7091,18 +7269,18 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>465</v>
+        <v>434</v>
       </c>
       <c r="C94" t="s">
-        <v>466</v>
+        <v>435</v>
       </c>
       <c r="D94" t="s">
-        <v>467</v>
+        <v>436</v>
       </c>
       <c r="E94" t="s">
         <v>9</v>
       </c>
-      <c r="F94" t="s">
+      <c r="F94" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G94" t="s">
@@ -7114,18 +7292,18 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>468</v>
+        <v>437</v>
       </c>
       <c r="C95" t="s">
-        <v>469</v>
+        <v>438</v>
       </c>
       <c r="D95" t="s">
-        <v>470</v>
+        <v>439</v>
       </c>
       <c r="E95" t="s">
         <v>9</v>
       </c>
-      <c r="F95" t="s">
+      <c r="F95" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G95" t="s">
@@ -7137,18 +7315,18 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>471</v>
+        <v>440</v>
       </c>
       <c r="C96" t="s">
-        <v>472</v>
+        <v>441</v>
       </c>
       <c r="D96" t="s">
-        <v>473</v>
+        <v>442</v>
       </c>
       <c r="E96" t="s">
         <v>9</v>
       </c>
-      <c r="F96" t="s">
+      <c r="F96" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G96" t="s">
@@ -7160,18 +7338,18 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>474</v>
+        <v>443</v>
       </c>
       <c r="C97" t="s">
-        <v>475</v>
+        <v>444</v>
       </c>
       <c r="D97" t="s">
-        <v>476</v>
+        <v>445</v>
       </c>
       <c r="E97" t="s">
         <v>9</v>
       </c>
-      <c r="F97" t="s">
+      <c r="F97" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G97" t="s">
@@ -7183,18 +7361,18 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>477</v>
+        <v>446</v>
       </c>
       <c r="C98" t="s">
-        <v>478</v>
+        <v>447</v>
       </c>
       <c r="D98" t="s">
-        <v>479</v>
+        <v>448</v>
       </c>
       <c r="E98" t="s">
         <v>9</v>
       </c>
-      <c r="F98" t="s">
+      <c r="F98" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G98" t="s">
@@ -7206,18 +7384,18 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>480</v>
+        <v>449</v>
       </c>
       <c r="C99" t="s">
-        <v>481</v>
+        <v>450</v>
       </c>
       <c r="D99" t="s">
-        <v>482</v>
+        <v>451</v>
       </c>
       <c r="E99" t="s">
         <v>9</v>
       </c>
-      <c r="F99" t="s">
+      <c r="F99" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G99" t="s">
@@ -7229,18 +7407,18 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>483</v>
+        <v>452</v>
       </c>
       <c r="C100" t="s">
-        <v>484</v>
+        <v>453</v>
       </c>
       <c r="D100" t="s">
-        <v>485</v>
+        <v>454</v>
       </c>
       <c r="E100" t="s">
         <v>9</v>
       </c>
-      <c r="F100" t="s">
+      <c r="F100" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G100" t="s">
@@ -7252,18 +7430,18 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>486</v>
+        <v>455</v>
       </c>
       <c r="C101" t="s">
-        <v>487</v>
+        <v>456</v>
       </c>
       <c r="D101" t="s">
-        <v>488</v>
+        <v>457</v>
       </c>
       <c r="E101" t="s">
         <v>9</v>
       </c>
-      <c r="F101" t="s">
+      <c r="F101" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G101" t="s">
@@ -7275,18 +7453,18 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>489</v>
+        <v>458</v>
       </c>
       <c r="C102" t="s">
-        <v>490</v>
+        <v>459</v>
       </c>
       <c r="D102" t="s">
-        <v>491</v>
+        <v>460</v>
       </c>
       <c r="E102" t="s">
         <v>9</v>
       </c>
-      <c r="F102" t="s">
+      <c r="F102" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G102" t="s">
@@ -7298,18 +7476,18 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>492</v>
+        <v>461</v>
       </c>
       <c r="C103" t="s">
-        <v>493</v>
+        <v>462</v>
       </c>
       <c r="D103" t="s">
-        <v>494</v>
+        <v>463</v>
       </c>
       <c r="E103" t="s">
         <v>9</v>
       </c>
-      <c r="F103" t="s">
+      <c r="F103" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G103" t="s">
@@ -7321,18 +7499,18 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>495</v>
+        <v>464</v>
       </c>
       <c r="C104" t="s">
-        <v>496</v>
+        <v>465</v>
       </c>
       <c r="D104" t="s">
-        <v>497</v>
+        <v>466</v>
       </c>
       <c r="E104" t="s">
         <v>9</v>
       </c>
-      <c r="F104" t="s">
+      <c r="F104" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G104" t="s">
@@ -7344,18 +7522,18 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>498</v>
+        <v>467</v>
       </c>
       <c r="C105" t="s">
-        <v>499</v>
+        <v>468</v>
       </c>
       <c r="D105" t="s">
-        <v>500</v>
+        <v>469</v>
       </c>
       <c r="E105" t="s">
         <v>9</v>
       </c>
-      <c r="F105" t="s">
+      <c r="F105" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G105" t="s">
@@ -7367,18 +7545,18 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>501</v>
+        <v>470</v>
       </c>
       <c r="C106" t="s">
-        <v>502</v>
+        <v>471</v>
       </c>
       <c r="D106" t="s">
-        <v>503</v>
+        <v>472</v>
       </c>
       <c r="E106" t="s">
         <v>9</v>
       </c>
-      <c r="F106" t="s">
+      <c r="F106" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G106" t="s">
@@ -7390,18 +7568,18 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>504</v>
+        <v>473</v>
       </c>
       <c r="C107" t="s">
-        <v>505</v>
+        <v>474</v>
       </c>
       <c r="D107" t="s">
-        <v>506</v>
+        <v>475</v>
       </c>
       <c r="E107" t="s">
         <v>9</v>
       </c>
-      <c r="F107" t="s">
+      <c r="F107" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G107" t="s">
@@ -7413,18 +7591,18 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>507</v>
+        <v>476</v>
       </c>
       <c r="C108" t="s">
-        <v>508</v>
+        <v>477</v>
       </c>
       <c r="D108" t="s">
-        <v>509</v>
+        <v>478</v>
       </c>
       <c r="E108" t="s">
         <v>9</v>
       </c>
-      <c r="F108" t="s">
+      <c r="F108" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G108" t="s">
@@ -7436,18 +7614,18 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>510</v>
+        <v>479</v>
       </c>
       <c r="C109" t="s">
-        <v>511</v>
+        <v>480</v>
       </c>
       <c r="D109" t="s">
-        <v>512</v>
+        <v>481</v>
       </c>
       <c r="E109" t="s">
         <v>9</v>
       </c>
-      <c r="F109" t="s">
+      <c r="F109" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G109" t="s">
@@ -7459,18 +7637,18 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>513</v>
+        <v>482</v>
       </c>
       <c r="C110" t="s">
-        <v>514</v>
+        <v>483</v>
       </c>
       <c r="D110" t="s">
-        <v>515</v>
+        <v>484</v>
       </c>
       <c r="E110" t="s">
         <v>9</v>
       </c>
-      <c r="F110" t="s">
+      <c r="F110" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G110" t="s">
@@ -7482,18 +7660,18 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>516</v>
+        <v>485</v>
       </c>
       <c r="C111" t="s">
-        <v>517</v>
+        <v>486</v>
       </c>
       <c r="D111" t="s">
-        <v>518</v>
+        <v>487</v>
       </c>
       <c r="E111" t="s">
         <v>9</v>
       </c>
-      <c r="F111" t="s">
+      <c r="F111" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G111" t="s">
@@ -7505,18 +7683,18 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>519</v>
+        <v>488</v>
       </c>
       <c r="C112" t="s">
-        <v>520</v>
+        <v>489</v>
       </c>
       <c r="D112" t="s">
-        <v>521</v>
+        <v>490</v>
       </c>
       <c r="E112" t="s">
         <v>9</v>
       </c>
-      <c r="F112" t="s">
+      <c r="F112" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G112" t="s">
@@ -7528,18 +7706,18 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>522</v>
+        <v>491</v>
       </c>
       <c r="C113" t="s">
-        <v>523</v>
+        <v>492</v>
       </c>
       <c r="D113" t="s">
-        <v>524</v>
+        <v>493</v>
       </c>
       <c r="E113" t="s">
         <v>9</v>
       </c>
-      <c r="F113" t="s">
+      <c r="F113" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G113" t="s">
@@ -7551,18 +7729,18 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>525</v>
+        <v>494</v>
       </c>
       <c r="C114" t="s">
-        <v>526</v>
+        <v>495</v>
       </c>
       <c r="D114" t="s">
-        <v>527</v>
+        <v>496</v>
       </c>
       <c r="E114" t="s">
         <v>9</v>
       </c>
-      <c r="F114" t="s">
+      <c r="F114" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G114" t="s">
@@ -7574,18 +7752,18 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>528</v>
+        <v>497</v>
       </c>
       <c r="C115" t="s">
-        <v>529</v>
+        <v>498</v>
       </c>
       <c r="D115" t="s">
-        <v>530</v>
+        <v>499</v>
       </c>
       <c r="E115" t="s">
         <v>9</v>
       </c>
-      <c r="F115" t="s">
+      <c r="F115" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G115" t="s">
@@ -7597,18 +7775,18 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>531</v>
+        <v>500</v>
       </c>
       <c r="C116" t="s">
-        <v>532</v>
+        <v>501</v>
       </c>
       <c r="D116" t="s">
-        <v>533</v>
+        <v>502</v>
       </c>
       <c r="E116" t="s">
         <v>9</v>
       </c>
-      <c r="F116" t="s">
+      <c r="F116" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G116" t="s">
@@ -7620,18 +7798,18 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>534</v>
+        <v>503</v>
       </c>
       <c r="C117" t="s">
-        <v>535</v>
+        <v>504</v>
       </c>
       <c r="D117" t="s">
-        <v>536</v>
+        <v>505</v>
       </c>
       <c r="E117" t="s">
         <v>9</v>
       </c>
-      <c r="F117" t="s">
+      <c r="F117" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G117" t="s">
@@ -7643,18 +7821,18 @@
         <v>1</v>
       </c>
       <c r="B118" t="s">
-        <v>537</v>
+        <v>506</v>
       </c>
       <c r="C118" t="s">
-        <v>537</v>
+        <v>506</v>
       </c>
       <c r="D118" t="s">
-        <v>538</v>
+        <v>507</v>
       </c>
       <c r="E118" t="s">
-        <v>180</v>
-      </c>
-      <c r="F118" t="s">
+        <v>149</v>
+      </c>
+      <c r="F118" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G118" t="s">
@@ -7666,18 +7844,18 @@
         <v>2</v>
       </c>
       <c r="B119" t="s">
-        <v>539</v>
+        <v>508</v>
       </c>
       <c r="C119" t="s">
-        <v>539</v>
+        <v>508</v>
       </c>
       <c r="D119" t="s">
-        <v>540</v>
+        <v>509</v>
       </c>
       <c r="E119" t="s">
-        <v>180</v>
-      </c>
-      <c r="F119" t="s">
+        <v>149</v>
+      </c>
+      <c r="F119" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G119" t="s">
@@ -7689,18 +7867,18 @@
         <v>3</v>
       </c>
       <c r="B120" t="s">
-        <v>541</v>
+        <v>510</v>
       </c>
       <c r="C120" t="s">
-        <v>541</v>
+        <v>510</v>
       </c>
       <c r="D120" t="s">
-        <v>542</v>
+        <v>511</v>
       </c>
       <c r="E120" t="s">
-        <v>180</v>
-      </c>
-      <c r="F120" t="s">
+        <v>149</v>
+      </c>
+      <c r="F120" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G120" t="s">
@@ -7712,18 +7890,18 @@
         <v>4</v>
       </c>
       <c r="B121" t="s">
-        <v>391</v>
+        <v>360</v>
       </c>
       <c r="C121" t="s">
-        <v>391</v>
+        <v>360</v>
       </c>
       <c r="D121" t="s">
-        <v>392</v>
+        <v>361</v>
       </c>
       <c r="E121" t="s">
-        <v>180</v>
-      </c>
-      <c r="F121" t="s">
+        <v>149</v>
+      </c>
+      <c r="F121" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G121" t="s">
@@ -7735,18 +7913,18 @@
         <v>5</v>
       </c>
       <c r="B122" t="s">
-        <v>543</v>
+        <v>512</v>
       </c>
       <c r="C122" t="s">
-        <v>543</v>
+        <v>512</v>
       </c>
       <c r="D122" t="s">
-        <v>544</v>
+        <v>513</v>
       </c>
       <c r="E122" t="s">
-        <v>180</v>
-      </c>
-      <c r="F122" t="s">
+        <v>149</v>
+      </c>
+      <c r="F122" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G122" t="s">
@@ -7758,18 +7936,18 @@
         <v>6</v>
       </c>
       <c r="B123" t="s">
-        <v>545</v>
+        <v>514</v>
       </c>
       <c r="C123" t="s">
-        <v>545</v>
+        <v>514</v>
       </c>
       <c r="D123" t="s">
-        <v>546</v>
+        <v>515</v>
       </c>
       <c r="E123" t="s">
-        <v>180</v>
-      </c>
-      <c r="F123" t="s">
+        <v>149</v>
+      </c>
+      <c r="F123" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G123" t="s">
@@ -7781,18 +7959,18 @@
         <v>7</v>
       </c>
       <c r="B124" t="s">
-        <v>547</v>
+        <v>516</v>
       </c>
       <c r="C124" t="s">
-        <v>547</v>
+        <v>516</v>
       </c>
       <c r="D124" t="s">
-        <v>548</v>
+        <v>517</v>
       </c>
       <c r="E124" t="s">
-        <v>180</v>
-      </c>
-      <c r="F124" t="s">
+        <v>149</v>
+      </c>
+      <c r="F124" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G124" t="s">
@@ -7803,7 +7981,7 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G124" numberStoredAsText="1"/>
+    <ignoredError sqref="A2:G124 B1:G1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -7841,13 +8019,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>549</v>
+        <v>518</v>
       </c>
       <c r="C2" t="s">
-        <v>550</v>
+        <v>519</v>
       </c>
       <c r="D2" t="s">
-        <v>551</v>
+        <v>520</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -7864,13 +8042,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>552</v>
+        <v>521</v>
       </c>
       <c r="C3" t="s">
-        <v>553</v>
+        <v>522</v>
       </c>
       <c r="D3" t="s">
-        <v>554</v>
+        <v>523</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -7887,13 +8065,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>555</v>
+        <v>524</v>
       </c>
       <c r="C4" t="s">
-        <v>556</v>
+        <v>525</v>
       </c>
       <c r="D4" t="s">
-        <v>557</v>
+        <v>526</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -7910,13 +8088,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>558</v>
+        <v>527</v>
       </c>
       <c r="C5" t="s">
-        <v>559</v>
+        <v>528</v>
       </c>
       <c r="D5" t="s">
-        <v>560</v>
+        <v>529</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -7933,13 +8111,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>561</v>
+        <v>530</v>
       </c>
       <c r="C6" t="s">
-        <v>562</v>
+        <v>531</v>
       </c>
       <c r="D6" t="s">
-        <v>563</v>
+        <v>532</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -7956,13 +8134,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>564</v>
+        <v>533</v>
       </c>
       <c r="C7" t="s">
-        <v>565</v>
+        <v>534</v>
       </c>
       <c r="D7" t="s">
-        <v>566</v>
+        <v>535</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -7979,13 +8157,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>567</v>
+        <v>536</v>
       </c>
       <c r="C8" t="s">
-        <v>568</v>
+        <v>537</v>
       </c>
       <c r="D8" t="s">
-        <v>569</v>
+        <v>538</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -8002,13 +8180,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>570</v>
+        <v>539</v>
       </c>
       <c r="C9" t="s">
-        <v>571</v>
+        <v>540</v>
       </c>
       <c r="D9" t="s">
-        <v>572</v>
+        <v>541</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -8025,13 +8203,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>573</v>
+        <v>542</v>
       </c>
       <c r="C10" t="s">
-        <v>574</v>
+        <v>543</v>
       </c>
       <c r="D10" t="s">
-        <v>575</v>
+        <v>544</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -8048,13 +8226,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>576</v>
+        <v>545</v>
       </c>
       <c r="C11" t="s">
-        <v>577</v>
+        <v>546</v>
       </c>
       <c r="D11" t="s">
-        <v>578</v>
+        <v>547</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -8071,13 +8249,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>579</v>
+        <v>548</v>
       </c>
       <c r="C12" t="s">
-        <v>580</v>
+        <v>549</v>
       </c>
       <c r="D12" t="s">
-        <v>581</v>
+        <v>550</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -8094,13 +8272,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>582</v>
+        <v>551</v>
       </c>
       <c r="C13" t="s">
-        <v>583</v>
+        <v>552</v>
       </c>
       <c r="D13" t="s">
-        <v>584</v>
+        <v>553</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -8117,13 +8295,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>585</v>
+        <v>554</v>
       </c>
       <c r="C14" t="s">
-        <v>586</v>
+        <v>555</v>
       </c>
       <c r="D14" t="s">
-        <v>587</v>
+        <v>556</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -8140,13 +8318,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>588</v>
+        <v>557</v>
       </c>
       <c r="C15" t="s">
-        <v>589</v>
+        <v>558</v>
       </c>
       <c r="D15" t="s">
-        <v>590</v>
+        <v>559</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -8163,13 +8341,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>591</v>
+        <v>560</v>
       </c>
       <c r="C16" t="s">
-        <v>592</v>
+        <v>561</v>
       </c>
       <c r="D16" t="s">
-        <v>593</v>
+        <v>562</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -8223,13 +8401,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>594</v>
+        <v>563</v>
       </c>
       <c r="C2" t="s">
-        <v>595</v>
+        <v>564</v>
       </c>
       <c r="D2" t="s">
-        <v>596</v>
+        <v>565</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -8246,13 +8424,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>597</v>
+        <v>566</v>
       </c>
       <c r="C3" t="s">
-        <v>598</v>
+        <v>567</v>
       </c>
       <c r="D3" t="s">
-        <v>599</v>
+        <v>568</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -8269,13 +8447,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>600</v>
+        <v>569</v>
       </c>
       <c r="C4" t="s">
-        <v>601</v>
+        <v>570</v>
       </c>
       <c r="D4" t="s">
-        <v>602</v>
+        <v>571</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -8292,13 +8470,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>603</v>
+        <v>572</v>
       </c>
       <c r="C5" t="s">
-        <v>604</v>
+        <v>573</v>
       </c>
       <c r="D5" t="s">
-        <v>605</v>
+        <v>574</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -8315,13 +8493,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>606</v>
+        <v>575</v>
       </c>
       <c r="C6" t="s">
-        <v>607</v>
+        <v>576</v>
       </c>
       <c r="D6" t="s">
-        <v>608</v>
+        <v>577</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -8338,13 +8516,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>609</v>
+        <v>578</v>
       </c>
       <c r="C7" t="s">
-        <v>610</v>
+        <v>579</v>
       </c>
       <c r="D7" t="s">
-        <v>611</v>
+        <v>580</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -8361,13 +8539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>612</v>
+        <v>581</v>
       </c>
       <c r="C8" t="s">
-        <v>613</v>
+        <v>582</v>
       </c>
       <c r="D8" t="s">
-        <v>614</v>
+        <v>583</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -8384,13 +8562,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>615</v>
+        <v>584</v>
       </c>
       <c r="C9" t="s">
-        <v>616</v>
+        <v>585</v>
       </c>
       <c r="D9" t="s">
-        <v>617</v>
+        <v>586</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -8407,13 +8585,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>618</v>
+        <v>587</v>
       </c>
       <c r="C10" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
       <c r="D10" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -8430,13 +8608,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>621</v>
+        <v>590</v>
       </c>
       <c r="C11" t="s">
-        <v>622</v>
+        <v>591</v>
       </c>
       <c r="D11" t="s">
-        <v>623</v>
+        <v>592</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -8453,13 +8631,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>624</v>
+        <v>593</v>
       </c>
       <c r="C12" t="s">
-        <v>625</v>
+        <v>594</v>
       </c>
       <c r="D12" t="s">
-        <v>626</v>
+        <v>595</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -8476,13 +8654,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>627</v>
+        <v>596</v>
       </c>
       <c r="C13" t="s">
-        <v>628</v>
+        <v>597</v>
       </c>
       <c r="D13" t="s">
-        <v>629</v>
+        <v>598</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -8499,13 +8677,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>630</v>
+        <v>599</v>
       </c>
       <c r="C14" t="s">
-        <v>631</v>
+        <v>600</v>
       </c>
       <c r="D14" t="s">
-        <v>632</v>
+        <v>601</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -8522,13 +8700,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>633</v>
+        <v>602</v>
       </c>
       <c r="C15" t="s">
-        <v>634</v>
+        <v>603</v>
       </c>
       <c r="D15" t="s">
-        <v>635</v>
+        <v>604</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -8545,13 +8723,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>636</v>
+        <v>605</v>
       </c>
       <c r="C16" t="s">
-        <v>637</v>
+        <v>606</v>
       </c>
       <c r="D16" t="s">
-        <v>638</v>
+        <v>607</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -8568,13 +8746,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>639</v>
+        <v>608</v>
       </c>
       <c r="C17" t="s">
-        <v>640</v>
+        <v>609</v>
       </c>
       <c r="D17" t="s">
-        <v>641</v>
+        <v>610</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -8591,13 +8769,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>642</v>
+        <v>611</v>
       </c>
       <c r="C18" t="s">
-        <v>643</v>
+        <v>612</v>
       </c>
       <c r="D18" t="s">
-        <v>644</v>
+        <v>613</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -8614,13 +8792,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>645</v>
+        <v>614</v>
       </c>
       <c r="C19" t="s">
-        <v>646</v>
+        <v>615</v>
       </c>
       <c r="D19" t="s">
-        <v>647</v>
+        <v>616</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
@@ -8637,13 +8815,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>648</v>
+        <v>617</v>
       </c>
       <c r="C20" t="s">
-        <v>649</v>
+        <v>618</v>
       </c>
       <c r="D20" t="s">
-        <v>650</v>
+        <v>619</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
@@ -8660,13 +8838,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>651</v>
+        <v>620</v>
       </c>
       <c r="C21" t="s">
-        <v>652</v>
+        <v>621</v>
       </c>
       <c r="D21" t="s">
-        <v>653</v>
+        <v>622</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -8683,13 +8861,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>654</v>
+        <v>623</v>
       </c>
       <c r="C22" t="s">
-        <v>655</v>
+        <v>624</v>
       </c>
       <c r="D22" t="s">
-        <v>656</v>
+        <v>625</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
@@ -8706,13 +8884,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>657</v>
+        <v>626</v>
       </c>
       <c r="C23" t="s">
-        <v>658</v>
+        <v>627</v>
       </c>
       <c r="D23" t="s">
-        <v>659</v>
+        <v>628</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
@@ -8729,13 +8907,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>660</v>
+        <v>629</v>
       </c>
       <c r="C24" t="s">
-        <v>661</v>
+        <v>630</v>
       </c>
       <c r="D24" t="s">
-        <v>662</v>
+        <v>631</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
@@ -8752,13 +8930,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>663</v>
+        <v>632</v>
       </c>
       <c r="C25" t="s">
-        <v>664</v>
+        <v>633</v>
       </c>
       <c r="D25" t="s">
-        <v>665</v>
+        <v>634</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
@@ -8775,13 +8953,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>666</v>
+        <v>635</v>
       </c>
       <c r="C26" t="s">
-        <v>667</v>
+        <v>636</v>
       </c>
       <c r="D26" t="s">
-        <v>668</v>
+        <v>637</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
@@ -8798,13 +8976,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>669</v>
+        <v>638</v>
       </c>
       <c r="C27" t="s">
-        <v>670</v>
+        <v>639</v>
       </c>
       <c r="D27" t="s">
-        <v>671</v>
+        <v>640</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
@@ -8821,13 +8999,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>672</v>
+        <v>641</v>
       </c>
       <c r="C28" t="s">
-        <v>673</v>
+        <v>642</v>
       </c>
       <c r="D28" t="s">
-        <v>674</v>
+        <v>643</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
@@ -8844,13 +9022,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>675</v>
+        <v>644</v>
       </c>
       <c r="C29" t="s">
-        <v>676</v>
+        <v>645</v>
       </c>
       <c r="D29" t="s">
-        <v>677</v>
+        <v>646</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
@@ -8867,13 +9045,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>678</v>
+        <v>647</v>
       </c>
       <c r="C30" t="s">
-        <v>679</v>
+        <v>648</v>
       </c>
       <c r="D30" t="s">
-        <v>680</v>
+        <v>649</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
@@ -8890,13 +9068,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>681</v>
+        <v>650</v>
       </c>
       <c r="C31" t="s">
-        <v>682</v>
+        <v>651</v>
       </c>
       <c r="D31" t="s">
-        <v>683</v>
+        <v>652</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
@@ -8913,13 +9091,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>684</v>
+        <v>653</v>
       </c>
       <c r="C32" t="s">
-        <v>685</v>
+        <v>654</v>
       </c>
       <c r="D32" t="s">
-        <v>686</v>
+        <v>655</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
@@ -8936,13 +9114,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>687</v>
+        <v>656</v>
       </c>
       <c r="C33" t="s">
-        <v>688</v>
+        <v>657</v>
       </c>
       <c r="D33" t="s">
-        <v>689</v>
+        <v>658</v>
       </c>
       <c r="E33" t="s">
         <v>9</v>
@@ -8959,13 +9137,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>690</v>
+        <v>659</v>
       </c>
       <c r="C34" t="s">
-        <v>691</v>
+        <v>660</v>
       </c>
       <c r="D34" t="s">
-        <v>692</v>
+        <v>661</v>
       </c>
       <c r="E34" t="s">
         <v>9</v>
@@ -8982,13 +9160,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>693</v>
+        <v>662</v>
       </c>
       <c r="C35" t="s">
-        <v>694</v>
+        <v>663</v>
       </c>
       <c r="D35" t="s">
-        <v>695</v>
+        <v>664</v>
       </c>
       <c r="E35" t="s">
         <v>9</v>
@@ -9005,13 +9183,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>696</v>
+        <v>665</v>
       </c>
       <c r="C36" t="s">
-        <v>696</v>
+        <v>665</v>
       </c>
       <c r="D36" t="s">
-        <v>697</v>
+        <v>666</v>
       </c>
       <c r="E36" t="s">
         <v>9</v>
@@ -9028,13 +9206,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>698</v>
+        <v>667</v>
       </c>
       <c r="C37" t="s">
-        <v>699</v>
+        <v>668</v>
       </c>
       <c r="D37" t="s">
-        <v>700</v>
+        <v>669</v>
       </c>
       <c r="E37" t="s">
         <v>9</v>
@@ -9051,13 +9229,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>701</v>
+        <v>670</v>
       </c>
       <c r="C38" t="s">
-        <v>702</v>
+        <v>671</v>
       </c>
       <c r="D38" t="s">
-        <v>703</v>
+        <v>672</v>
       </c>
       <c r="E38" t="s">
         <v>9</v>
@@ -9074,13 +9252,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>704</v>
+        <v>673</v>
       </c>
       <c r="C39" t="s">
-        <v>705</v>
+        <v>674</v>
       </c>
       <c r="D39" t="s">
-        <v>706</v>
+        <v>675</v>
       </c>
       <c r="E39" t="s">
         <v>9</v>
@@ -9097,13 +9275,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>707</v>
+        <v>676</v>
       </c>
       <c r="C40" t="s">
-        <v>708</v>
+        <v>677</v>
       </c>
       <c r="D40" t="s">
-        <v>709</v>
+        <v>678</v>
       </c>
       <c r="E40" t="s">
         <v>9</v>
@@ -9120,13 +9298,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>710</v>
+        <v>679</v>
       </c>
       <c r="C41" t="s">
-        <v>711</v>
+        <v>680</v>
       </c>
       <c r="D41" t="s">
-        <v>712</v>
+        <v>681</v>
       </c>
       <c r="E41" t="s">
         <v>9</v>
@@ -9143,13 +9321,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>713</v>
+        <v>682</v>
       </c>
       <c r="C42" t="s">
-        <v>714</v>
+        <v>683</v>
       </c>
       <c r="D42" t="s">
-        <v>715</v>
+        <v>684</v>
       </c>
       <c r="E42" t="s">
         <v>9</v>
@@ -9166,13 +9344,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>716</v>
+        <v>685</v>
       </c>
       <c r="C43" t="s">
-        <v>716</v>
+        <v>685</v>
       </c>
       <c r="D43" t="s">
-        <v>717</v>
+        <v>686</v>
       </c>
       <c r="E43" t="s">
         <v>9</v>
@@ -9189,13 +9367,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>718</v>
+        <v>687</v>
       </c>
       <c r="C44" t="s">
-        <v>719</v>
+        <v>688</v>
       </c>
       <c r="D44" t="s">
-        <v>720</v>
+        <v>689</v>
       </c>
       <c r="E44" t="s">
         <v>9</v>
@@ -9212,13 +9390,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>721</v>
+        <v>690</v>
       </c>
       <c r="C45" t="s">
-        <v>722</v>
+        <v>691</v>
       </c>
       <c r="D45" t="s">
-        <v>723</v>
+        <v>692</v>
       </c>
       <c r="E45" t="s">
         <v>9</v>
@@ -9235,13 +9413,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>724</v>
+        <v>693</v>
       </c>
       <c r="C46" t="s">
-        <v>725</v>
+        <v>694</v>
       </c>
       <c r="D46" t="s">
-        <v>726</v>
+        <v>695</v>
       </c>
       <c r="E46" t="s">
         <v>9</v>
@@ -9258,13 +9436,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>727</v>
+        <v>696</v>
       </c>
       <c r="C47" t="s">
-        <v>728</v>
+        <v>697</v>
       </c>
       <c r="D47" t="s">
-        <v>729</v>
+        <v>698</v>
       </c>
       <c r="E47" t="s">
         <v>9</v>
@@ -9281,13 +9459,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>730</v>
+        <v>699</v>
       </c>
       <c r="C48" t="s">
-        <v>731</v>
+        <v>700</v>
       </c>
       <c r="D48" t="s">
-        <v>732</v>
+        <v>701</v>
       </c>
       <c r="E48" t="s">
         <v>9</v>
@@ -9304,13 +9482,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>733</v>
+        <v>702</v>
       </c>
       <c r="C49" t="s">
-        <v>733</v>
+        <v>702</v>
       </c>
       <c r="D49" t="s">
-        <v>734</v>
+        <v>703</v>
       </c>
       <c r="E49" t="s">
         <v>9</v>
@@ -9327,13 +9505,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>735</v>
+        <v>704</v>
       </c>
       <c r="C50" t="s">
-        <v>736</v>
+        <v>705</v>
       </c>
       <c r="D50" t="s">
-        <v>737</v>
+        <v>706</v>
       </c>
       <c r="E50" t="s">
         <v>9</v>
@@ -9350,13 +9528,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>738</v>
+        <v>707</v>
       </c>
       <c r="C51" t="s">
-        <v>739</v>
+        <v>708</v>
       </c>
       <c r="D51" t="s">
-        <v>740</v>
+        <v>709</v>
       </c>
       <c r="E51" t="s">
         <v>9</v>
@@ -9373,13 +9551,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>741</v>
+        <v>710</v>
       </c>
       <c r="C52" t="s">
-        <v>742</v>
+        <v>711</v>
       </c>
       <c r="D52" t="s">
-        <v>743</v>
+        <v>712</v>
       </c>
       <c r="E52" t="s">
         <v>9</v>
@@ -9396,13 +9574,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>744</v>
+        <v>713</v>
       </c>
       <c r="C53" t="s">
-        <v>745</v>
+        <v>714</v>
       </c>
       <c r="D53" t="s">
-        <v>746</v>
+        <v>715</v>
       </c>
       <c r="E53" t="s">
         <v>9</v>
@@ -9419,13 +9597,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>747</v>
+        <v>716</v>
       </c>
       <c r="C54" t="s">
-        <v>748</v>
+        <v>717</v>
       </c>
       <c r="D54" t="s">
-        <v>749</v>
+        <v>718</v>
       </c>
       <c r="E54" t="s">
         <v>9</v>
@@ -9442,13 +9620,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>750</v>
+        <v>719</v>
       </c>
       <c r="C55" t="s">
-        <v>751</v>
+        <v>720</v>
       </c>
       <c r="D55" t="s">
-        <v>752</v>
+        <v>721</v>
       </c>
       <c r="E55" t="s">
         <v>9</v>
@@ -9465,13 +9643,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>753</v>
+        <v>722</v>
       </c>
       <c r="C56" t="s">
-        <v>754</v>
+        <v>723</v>
       </c>
       <c r="D56" t="s">
-        <v>755</v>
+        <v>724</v>
       </c>
       <c r="E56" t="s">
         <v>9</v>
@@ -9488,13 +9666,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>756</v>
+        <v>725</v>
       </c>
       <c r="C57" t="s">
-        <v>757</v>
+        <v>726</v>
       </c>
       <c r="D57" t="s">
-        <v>758</v>
+        <v>727</v>
       </c>
       <c r="E57" t="s">
         <v>9</v>
@@ -9511,13 +9689,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>759</v>
+        <v>728</v>
       </c>
       <c r="C58" t="s">
-        <v>760</v>
+        <v>729</v>
       </c>
       <c r="D58" t="s">
-        <v>761</v>
+        <v>730</v>
       </c>
       <c r="E58" t="s">
         <v>9</v>
@@ -9534,13 +9712,13 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>762</v>
+        <v>731</v>
       </c>
       <c r="C59" t="s">
-        <v>763</v>
+        <v>732</v>
       </c>
       <c r="D59" t="s">
-        <v>764</v>
+        <v>733</v>
       </c>
       <c r="E59" t="s">
         <v>9</v>
@@ -9557,13 +9735,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>765</v>
+        <v>734</v>
       </c>
       <c r="C60" t="s">
-        <v>766</v>
+        <v>735</v>
       </c>
       <c r="D60" t="s">
-        <v>767</v>
+        <v>736</v>
       </c>
       <c r="E60" t="s">
         <v>9</v>
@@ -9580,13 +9758,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>768</v>
+        <v>737</v>
       </c>
       <c r="C61" t="s">
-        <v>769</v>
+        <v>738</v>
       </c>
       <c r="D61" t="s">
-        <v>770</v>
+        <v>739</v>
       </c>
       <c r="E61" t="s">
         <v>9</v>
@@ -9603,13 +9781,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>771</v>
+        <v>740</v>
       </c>
       <c r="C62" t="s">
-        <v>772</v>
+        <v>741</v>
       </c>
       <c r="D62" t="s">
-        <v>773</v>
+        <v>742</v>
       </c>
       <c r="E62" t="s">
         <v>9</v>
@@ -9626,13 +9804,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>774</v>
+        <v>743</v>
       </c>
       <c r="C63" t="s">
-        <v>775</v>
+        <v>744</v>
       </c>
       <c r="D63" t="s">
-        <v>776</v>
+        <v>745</v>
       </c>
       <c r="E63" t="s">
         <v>9</v>
@@ -9649,13 +9827,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>777</v>
+        <v>746</v>
       </c>
       <c r="C64" t="s">
-        <v>778</v>
+        <v>747</v>
       </c>
       <c r="D64" t="s">
-        <v>779</v>
+        <v>748</v>
       </c>
       <c r="E64" t="s">
         <v>9</v>
@@ -9672,13 +9850,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>780</v>
+        <v>749</v>
       </c>
       <c r="C65" t="s">
-        <v>781</v>
+        <v>750</v>
       </c>
       <c r="D65" t="s">
-        <v>782</v>
+        <v>751</v>
       </c>
       <c r="E65" t="s">
         <v>9</v>
@@ -9695,13 +9873,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>783</v>
+        <v>752</v>
       </c>
       <c r="C66" t="s">
-        <v>784</v>
+        <v>753</v>
       </c>
       <c r="D66" t="s">
-        <v>785</v>
+        <v>754</v>
       </c>
       <c r="E66" t="s">
         <v>9</v>
@@ -9718,13 +9896,13 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>786</v>
+        <v>755</v>
       </c>
       <c r="C67" t="s">
-        <v>787</v>
+        <v>756</v>
       </c>
       <c r="D67" t="s">
-        <v>788</v>
+        <v>757</v>
       </c>
       <c r="E67" t="s">
         <v>9</v>
@@ -9741,13 +9919,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>789</v>
+        <v>758</v>
       </c>
       <c r="C68" t="s">
-        <v>790</v>
+        <v>759</v>
       </c>
       <c r="D68" t="s">
-        <v>791</v>
+        <v>760</v>
       </c>
       <c r="E68" t="s">
         <v>9</v>
@@ -9764,13 +9942,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>792</v>
+        <v>761</v>
       </c>
       <c r="C69" t="s">
-        <v>793</v>
+        <v>762</v>
       </c>
       <c r="D69" t="s">
-        <v>794</v>
+        <v>763</v>
       </c>
       <c r="E69" t="s">
         <v>9</v>
@@ -9787,13 +9965,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>795</v>
+        <v>764</v>
       </c>
       <c r="C70" t="s">
-        <v>796</v>
+        <v>765</v>
       </c>
       <c r="D70" t="s">
-        <v>797</v>
+        <v>766</v>
       </c>
       <c r="E70" t="s">
         <v>9</v>
@@ -9810,13 +9988,13 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>798</v>
+        <v>767</v>
       </c>
       <c r="C71" t="s">
-        <v>799</v>
+        <v>768</v>
       </c>
       <c r="D71" t="s">
-        <v>800</v>
+        <v>769</v>
       </c>
       <c r="E71" t="s">
         <v>9</v>
@@ -9833,13 +10011,13 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>801</v>
+        <v>770</v>
       </c>
       <c r="C72" t="s">
-        <v>802</v>
+        <v>771</v>
       </c>
       <c r="D72" t="s">
-        <v>803</v>
+        <v>772</v>
       </c>
       <c r="E72" t="s">
         <v>9</v>
@@ -9856,13 +10034,13 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>804</v>
+        <v>773</v>
       </c>
       <c r="C73" t="s">
-        <v>805</v>
+        <v>774</v>
       </c>
       <c r="D73" t="s">
-        <v>806</v>
+        <v>775</v>
       </c>
       <c r="E73" t="s">
         <v>9</v>
@@ -9879,13 +10057,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>807</v>
+        <v>776</v>
       </c>
       <c r="C74" t="s">
-        <v>808</v>
+        <v>777</v>
       </c>
       <c r="D74" t="s">
-        <v>809</v>
+        <v>778</v>
       </c>
       <c r="E74" t="s">
         <v>9</v>
@@ -9902,13 +10080,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>810</v>
+        <v>779</v>
       </c>
       <c r="C75" t="s">
-        <v>811</v>
+        <v>780</v>
       </c>
       <c r="D75" t="s">
-        <v>812</v>
+        <v>781</v>
       </c>
       <c r="E75" t="s">
         <v>9</v>
@@ -9925,13 +10103,13 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>813</v>
+        <v>782</v>
       </c>
       <c r="C76" t="s">
-        <v>814</v>
+        <v>783</v>
       </c>
       <c r="D76" t="s">
-        <v>815</v>
+        <v>784</v>
       </c>
       <c r="E76" t="s">
         <v>9</v>
@@ -9948,13 +10126,13 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>816</v>
+        <v>785</v>
       </c>
       <c r="C77" t="s">
-        <v>817</v>
+        <v>786</v>
       </c>
       <c r="D77" t="s">
-        <v>818</v>
+        <v>787</v>
       </c>
       <c r="E77" t="s">
         <v>9</v>
@@ -9971,13 +10149,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>819</v>
+        <v>788</v>
       </c>
       <c r="C78" t="s">
-        <v>820</v>
+        <v>789</v>
       </c>
       <c r="D78" t="s">
-        <v>821</v>
+        <v>790</v>
       </c>
       <c r="E78" t="s">
         <v>9</v>
@@ -9994,13 +10172,13 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>822</v>
+        <v>791</v>
       </c>
       <c r="C79" t="s">
-        <v>823</v>
+        <v>792</v>
       </c>
       <c r="D79" t="s">
-        <v>824</v>
+        <v>793</v>
       </c>
       <c r="E79" t="s">
         <v>9</v>
@@ -10017,13 +10195,13 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>825</v>
+        <v>794</v>
       </c>
       <c r="C80" t="s">
-        <v>826</v>
+        <v>795</v>
       </c>
       <c r="D80" t="s">
-        <v>827</v>
+        <v>796</v>
       </c>
       <c r="E80" t="s">
         <v>9</v>
@@ -10040,13 +10218,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>828</v>
+        <v>797</v>
       </c>
       <c r="C81" t="s">
-        <v>829</v>
+        <v>798</v>
       </c>
       <c r="D81" t="s">
-        <v>830</v>
+        <v>799</v>
       </c>
       <c r="E81" t="s">
         <v>9</v>
@@ -10063,13 +10241,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>831</v>
+        <v>800</v>
       </c>
       <c r="C82" t="s">
-        <v>832</v>
+        <v>801</v>
       </c>
       <c r="D82" t="s">
-        <v>833</v>
+        <v>802</v>
       </c>
       <c r="E82" t="s">
         <v>9</v>
@@ -10086,13 +10264,13 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>834</v>
+        <v>803</v>
       </c>
       <c r="C83" t="s">
-        <v>835</v>
+        <v>804</v>
       </c>
       <c r="D83" t="s">
-        <v>836</v>
+        <v>805</v>
       </c>
       <c r="E83" t="s">
         <v>9</v>
@@ -10109,13 +10287,13 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>837</v>
+        <v>806</v>
       </c>
       <c r="C84" t="s">
-        <v>838</v>
+        <v>807</v>
       </c>
       <c r="D84" t="s">
-        <v>839</v>
+        <v>808</v>
       </c>
       <c r="E84" t="s">
         <v>9</v>
@@ -10132,13 +10310,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>840</v>
+        <v>809</v>
       </c>
       <c r="C85" t="s">
-        <v>841</v>
+        <v>810</v>
       </c>
       <c r="D85" t="s">
-        <v>842</v>
+        <v>811</v>
       </c>
       <c r="E85" t="s">
         <v>9</v>
@@ -10155,13 +10333,13 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>843</v>
+        <v>812</v>
       </c>
       <c r="C86" t="s">
-        <v>843</v>
+        <v>812</v>
       </c>
       <c r="D86" t="s">
-        <v>844</v>
+        <v>813</v>
       </c>
       <c r="E86" t="s">
         <v>9</v>
@@ -10178,13 +10356,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>845</v>
+        <v>814</v>
       </c>
       <c r="C87" t="s">
-        <v>846</v>
+        <v>815</v>
       </c>
       <c r="D87" t="s">
-        <v>847</v>
+        <v>816</v>
       </c>
       <c r="E87" t="s">
         <v>9</v>
@@ -10201,13 +10379,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>848</v>
+        <v>817</v>
       </c>
       <c r="C88" t="s">
-        <v>849</v>
+        <v>818</v>
       </c>
       <c r="D88" t="s">
-        <v>850</v>
+        <v>819</v>
       </c>
       <c r="E88" t="s">
         <v>9</v>
@@ -10224,13 +10402,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>851</v>
+        <v>820</v>
       </c>
       <c r="C89" t="s">
-        <v>851</v>
+        <v>820</v>
       </c>
       <c r="D89" t="s">
-        <v>852</v>
+        <v>821</v>
       </c>
       <c r="E89" t="s">
         <v>9</v>
@@ -10247,13 +10425,13 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>853</v>
+        <v>822</v>
       </c>
       <c r="C90" t="s">
-        <v>854</v>
+        <v>823</v>
       </c>
       <c r="D90" t="s">
-        <v>855</v>
+        <v>824</v>
       </c>
       <c r="E90" t="s">
         <v>9</v>
@@ -10270,13 +10448,13 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>856</v>
+        <v>825</v>
       </c>
       <c r="C91" t="s">
-        <v>857</v>
+        <v>826</v>
       </c>
       <c r="D91" t="s">
-        <v>858</v>
+        <v>827</v>
       </c>
       <c r="E91" t="s">
         <v>9</v>
@@ -10293,13 +10471,13 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>859</v>
+        <v>828</v>
       </c>
       <c r="C92" t="s">
-        <v>860</v>
+        <v>829</v>
       </c>
       <c r="D92" t="s">
-        <v>861</v>
+        <v>830</v>
       </c>
       <c r="E92" t="s">
         <v>9</v>
@@ -10316,13 +10494,13 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>862</v>
+        <v>831</v>
       </c>
       <c r="C93" t="s">
-        <v>863</v>
+        <v>832</v>
       </c>
       <c r="D93" t="s">
-        <v>864</v>
+        <v>833</v>
       </c>
       <c r="E93" t="s">
         <v>9</v>
@@ -10339,13 +10517,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>865</v>
+        <v>834</v>
       </c>
       <c r="C94" t="s">
-        <v>866</v>
+        <v>835</v>
       </c>
       <c r="D94" t="s">
-        <v>867</v>
+        <v>836</v>
       </c>
       <c r="E94" t="s">
         <v>9</v>
@@ -10362,13 +10540,13 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>868</v>
+        <v>837</v>
       </c>
       <c r="C95" t="s">
-        <v>869</v>
+        <v>838</v>
       </c>
       <c r="D95" t="s">
-        <v>870</v>
+        <v>839</v>
       </c>
       <c r="E95" t="s">
         <v>9</v>
@@ -10385,13 +10563,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>871</v>
+        <v>840</v>
       </c>
       <c r="C96" t="s">
-        <v>872</v>
+        <v>841</v>
       </c>
       <c r="D96" t="s">
-        <v>873</v>
+        <v>842</v>
       </c>
       <c r="E96" t="s">
         <v>9</v>
@@ -10408,13 +10586,13 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>874</v>
+        <v>843</v>
       </c>
       <c r="C97" t="s">
-        <v>874</v>
+        <v>843</v>
       </c>
       <c r="D97" t="s">
-        <v>875</v>
+        <v>844</v>
       </c>
       <c r="E97" t="s">
         <v>9</v>
@@ -10431,13 +10609,13 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>876</v>
+        <v>845</v>
       </c>
       <c r="C98" t="s">
-        <v>877</v>
+        <v>846</v>
       </c>
       <c r="D98" t="s">
-        <v>878</v>
+        <v>847</v>
       </c>
       <c r="E98" t="s">
         <v>9</v>
@@ -10454,13 +10632,13 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>879</v>
+        <v>848</v>
       </c>
       <c r="C99" t="s">
-        <v>880</v>
+        <v>849</v>
       </c>
       <c r="D99" t="s">
-        <v>881</v>
+        <v>850</v>
       </c>
       <c r="E99" t="s">
         <v>9</v>
@@ -10477,13 +10655,13 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>882</v>
+        <v>851</v>
       </c>
       <c r="C100" t="s">
-        <v>882</v>
+        <v>851</v>
       </c>
       <c r="D100" t="s">
-        <v>883</v>
+        <v>852</v>
       </c>
       <c r="E100" t="s">
         <v>9</v>
@@ -10500,13 +10678,13 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>884</v>
+        <v>853</v>
       </c>
       <c r="C101" t="s">
-        <v>885</v>
+        <v>854</v>
       </c>
       <c r="D101" t="s">
-        <v>886</v>
+        <v>855</v>
       </c>
       <c r="E101" t="s">
         <v>9</v>
@@ -10523,16 +10701,16 @@
         <v>1</v>
       </c>
       <c r="B102" t="s">
-        <v>887</v>
+        <v>856</v>
       </c>
       <c r="C102" t="s">
-        <v>887</v>
+        <v>856</v>
       </c>
       <c r="D102" t="s">
-        <v>888</v>
+        <v>857</v>
       </c>
       <c r="E102" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="F102" t="s">
         <v>11</v>
@@ -10546,16 +10724,16 @@
         <v>2</v>
       </c>
       <c r="B103" t="s">
-        <v>889</v>
+        <v>858</v>
       </c>
       <c r="C103" t="s">
-        <v>889</v>
+        <v>858</v>
       </c>
       <c r="D103" t="s">
-        <v>890</v>
+        <v>859</v>
       </c>
       <c r="E103" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="F103" t="s">
         <v>11</v>
@@ -10606,16 +10784,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>891</v>
+        <v>860</v>
       </c>
       <c r="C2" t="s">
-        <v>891</v>
+        <v>860</v>
       </c>
       <c r="D2" t="s">
-        <v>892</v>
+        <v>861</v>
       </c>
       <c r="E2" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="F2" t="s">
         <v>11</v>
@@ -10629,16 +10807,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>893</v>
+        <v>862</v>
       </c>
       <c r="C3" t="s">
-        <v>893</v>
+        <v>862</v>
       </c>
       <c r="D3" t="s">
-        <v>894</v>
+        <v>863</v>
       </c>
       <c r="E3" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="F3" t="s">
         <v>11</v>
@@ -10652,16 +10830,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>895</v>
+        <v>864</v>
       </c>
       <c r="C4" t="s">
-        <v>895</v>
+        <v>864</v>
       </c>
       <c r="D4" t="s">
-        <v>896</v>
+        <v>865</v>
       </c>
       <c r="E4" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="F4" t="s">
         <v>11</v>
@@ -10675,16 +10853,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>897</v>
+        <v>866</v>
       </c>
       <c r="C5" t="s">
-        <v>897</v>
+        <v>866</v>
       </c>
       <c r="D5" t="s">
-        <v>898</v>
+        <v>867</v>
       </c>
       <c r="E5" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="F5" t="s">
         <v>11</v>
@@ -10698,16 +10876,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>899</v>
+        <v>868</v>
       </c>
       <c r="C6" t="s">
-        <v>899</v>
+        <v>868</v>
       </c>
       <c r="D6" t="s">
-        <v>900</v>
+        <v>869</v>
       </c>
       <c r="E6" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="F6" t="s">
         <v>11</v>
@@ -10721,16 +10899,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>901</v>
+        <v>870</v>
       </c>
       <c r="C7" t="s">
-        <v>901</v>
+        <v>870</v>
       </c>
       <c r="D7" t="s">
-        <v>902</v>
+        <v>871</v>
       </c>
       <c r="E7" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="F7" t="s">
         <v>11</v>
@@ -10744,16 +10922,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>903</v>
+        <v>872</v>
       </c>
       <c r="C8" t="s">
-        <v>903</v>
+        <v>872</v>
       </c>
       <c r="D8" t="s">
-        <v>904</v>
+        <v>873</v>
       </c>
       <c r="E8" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="F8" t="s">
         <v>11</v>
@@ -10767,16 +10945,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>905</v>
+        <v>874</v>
       </c>
       <c r="C9" t="s">
-        <v>905</v>
+        <v>874</v>
       </c>
       <c r="D9" t="s">
-        <v>906</v>
+        <v>875</v>
       </c>
       <c r="E9" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="F9" t="s">
         <v>11</v>
@@ -10790,16 +10968,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>907</v>
+        <v>876</v>
       </c>
       <c r="C10" t="s">
-        <v>907</v>
+        <v>876</v>
       </c>
       <c r="D10" t="s">
-        <v>908</v>
+        <v>877</v>
       </c>
       <c r="E10" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="F10" t="s">
         <v>11</v>
@@ -10813,16 +10991,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>909</v>
+        <v>878</v>
       </c>
       <c r="C11" t="s">
-        <v>909</v>
+        <v>878</v>
       </c>
       <c r="D11" t="s">
-        <v>910</v>
+        <v>879</v>
       </c>
       <c r="E11" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="F11" t="s">
         <v>11</v>
@@ -10836,16 +11014,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>911</v>
+        <v>880</v>
       </c>
       <c r="C12" t="s">
-        <v>911</v>
+        <v>880</v>
       </c>
       <c r="D12" t="s">
-        <v>912</v>
+        <v>881</v>
       </c>
       <c r="E12" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="F12" t="s">
         <v>11</v>
@@ -10896,16 +11074,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>913</v>
+        <v>882</v>
       </c>
       <c r="C2" t="s">
-        <v>913</v>
+        <v>882</v>
       </c>
       <c r="D2" t="s">
-        <v>914</v>
+        <v>883</v>
       </c>
       <c r="E2" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="F2" t="s">
         <v>11</v>
@@ -10919,16 +11097,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>915</v>
+        <v>884</v>
       </c>
       <c r="C3" t="s">
-        <v>915</v>
+        <v>884</v>
       </c>
       <c r="D3" t="s">
-        <v>916</v>
+        <v>885</v>
       </c>
       <c r="E3" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="F3" t="s">
         <v>11</v>
